--- a/HQE Accelaration Requirement_06192026.xlsx
+++ b/HQE Accelaration Requirement_06192026.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020"/>
@@ -18,26 +18,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Requirement Consolidation'!$A$1:$L$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Workflow_Trigger Details'!$A$1:$F$18</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="144525"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -280,7 +265,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="637">
   <si>
     <t>Section - Generic - Campaign Overview</t>
   </si>
@@ -2870,6 +2855,60 @@
   </si>
   <si>
     <t>name 2</t>
+  </si>
+  <si>
+    <t>contracdicting drop downoptions</t>
+  </si>
+  <si>
+    <t>this is dependent on previouos option</t>
+  </si>
+  <si>
+    <t>wroing mapping to AOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wring mapping to AOR, wrong drop down, </t>
+  </si>
+  <si>
+    <t>wroing mapping to AOR, how is this a text, should be upload</t>
+  </si>
+  <si>
+    <t>wroing mapping to AOR, how is this text should be upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">needs ot be count, wroing mapping </t>
+  </si>
+  <si>
+    <t xml:space="preserve">unclear , need to triger CI form </t>
+  </si>
+  <si>
+    <t xml:space="preserve">needs to be data </t>
+  </si>
+  <si>
+    <t xml:space="preserve">needs to be date </t>
+  </si>
+  <si>
+    <t>what goes here?</t>
+  </si>
+  <si>
+    <t>how?</t>
+  </si>
+  <si>
+    <t>captured as upload what is exact process</t>
+  </si>
+  <si>
+    <t>text or upload?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reconfirm </t>
+  </si>
+  <si>
+    <t>not mentioned data type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if yes then, add another field </t>
+  </si>
+  <si>
+    <t>whats the outcome?</t>
   </si>
 </sst>
 </file>
@@ -2998,7 +3037,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3044,12 +3083,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3207,7 +3240,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3409,13 +3442,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3424,10 +3451,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3445,7 +3472,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3457,40 +3484,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -3503,34 +3530,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3545,88 +3620,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
-<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{0C7FC1A5-89AB-49AC-9D44-204D9ABBB931}">
-    <Anchor>
-      <Comment id="{349B11BE-9766-4493-9709-CB297EFCE6AA}"/>
-    </Anchor>
-    <History>
-      <Event time="2025-10-24T12:55:52.22" id="{1EE9C9D7-E04B-4B32-A35C-35E615EC7BE5}">
-        <Attribution userId="S::pvhja1@novartis.net::bb2d6fc5-c67c-42b0-a39a-b1f2e1ee4d9c" userName="Miah, Javid" userProvider="AD"/>
-        <Anchor>
-          <Comment id="{349B11BE-9766-4493-9709-CB297EFCE6AA}"/>
-        </Anchor>
-        <Create/>
-      </Event>
-      <Event time="2025-10-24T12:55:52.22" id="{12C743FC-2D3B-4DA1-82C1-7876B8E13B03}">
-        <Attribution userId="S::pvhja1@novartis.net::bb2d6fc5-c67c-42b0-a39a-b1f2e1ee4d9c" userName="Miah, Javid" userProvider="AD"/>
-        <Anchor>
-          <Comment id="{349B11BE-9766-4493-9709-CB297EFCE6AA}"/>
-        </Anchor>
-        <Assign userId="S::ARORAKA7@novartis.net::3d82822d-1cf7-44c4-9276-94ac755b2de0" userName="Arora, Kamal-1" userProvider="AD"/>
-      </Event>
-      <Event time="2025-10-24T12:55:52.22" id="{2A968F22-FBEE-47EB-9B00-84D3144748FD}">
-        <Attribution userId="S::pvhja1@novartis.net::bb2d6fc5-c67c-42b0-a39a-b1f2e1ee4d9c" userName="Miah, Javid" userProvider="AD"/>
-        <Anchor>
-          <Comment id="{349B11BE-9766-4493-9709-CB297EFCE6AA}"/>
-        </Anchor>
-        <SetTitle title="Javid: @Arora, Kamal-1 Model based: Utilize predictive analytics and machine learning to automate the next best action (message), best channel and ideal timing for audience segments. Ad Hoc: Targeted one-off email sends triggered by specific needs or …"/>
-      </Event>
-    </History>
-  </Task>
-</Tasks>
-</file>
-
-<file path=xl/documenttasks/documenttask2.xml><?xml version="1.0" encoding="utf-8"?>
-<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{A70C6C6F-388F-45B0-A811-50C9A9B3513F}">
-    <Anchor>
-      <Comment id="{1A6CE08A-8E87-4150-AC3E-567781FC2317}"/>
-    </Anchor>
-    <History>
-      <Event time="2025-10-24T12:55:52.22" id="{1EE9C9D7-E04B-4B32-A35C-35E615EC7BE5}">
-        <Attribution userId="S::pvhja1@novartis.net::bb2d6fc5-c67c-42b0-a39a-b1f2e1ee4d9c" userName="Miah, Javid" userProvider="AD"/>
-        <Anchor>
-          <Comment id="{1A6CE08A-8E87-4150-AC3E-567781FC2317}"/>
-        </Anchor>
-        <Create/>
-      </Event>
-      <Event time="2025-10-24T12:55:52.22" id="{12C743FC-2D3B-4DA1-82C1-7876B8E13B03}">
-        <Attribution userId="S::pvhja1@novartis.net::bb2d6fc5-c67c-42b0-a39a-b1f2e1ee4d9c" userName="Miah, Javid" userProvider="AD"/>
-        <Anchor>
-          <Comment id="{1A6CE08A-8E87-4150-AC3E-567781FC2317}"/>
-        </Anchor>
-        <Assign userId="S::ARORAKA7@novartis.net::3d82822d-1cf7-44c4-9276-94ac755b2de0" userName="Arora, Kamal-1" userProvider="AD"/>
-      </Event>
-      <Event time="2025-10-24T12:55:52.22" id="{2A968F22-FBEE-47EB-9B00-84D3144748FD}">
-        <Attribution userId="S::pvhja1@novartis.net::bb2d6fc5-c67c-42b0-a39a-b1f2e1ee4d9c" userName="Miah, Javid" userProvider="AD"/>
-        <Anchor>
-          <Comment id="{1A6CE08A-8E87-4150-AC3E-567781FC2317}"/>
-        </Anchor>
-        <SetTitle title="Javid: @Arora, Kamal-1 Model based: Utilize predictive analytics and machine learning to automate the next best action (message), best channel and ideal timing for audience segments. Ad Hoc: Targeted one-off email sends triggered by specific needs or …"/>
-      </Event>
-    </History>
-  </Task>
-</Tasks>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Arora, Kamal-1" id="{74FF87B2-1D80-4853-9B2F-A6139ADF2B26}" userId="ARORAKA7@novartis.net" providerId="PeoplePicker"/>
-  <person displayName="C, Akshay Kumar" id="{640FEB8E-85D3-4E0D-B758-FCE42ED412AC}" userId="S::CAK1@novartis.net::1c4b5294-4194-467d-9581-98403b458099" providerId="AD"/>
-  <person displayName="Miah, Javid" id="{0B1E5331-89E5-4E56-B252-A4F43E545167}" userId="S::PVHJA1@novartis.net::bb2d6fc5-c67c-42b0-a39a-b1f2e1ee4d9c" providerId="AD"/>
-  <person displayName="Miah, Javid" id="{E75BCEEB-DF11-46FF-B89C-3A408FA07791}" userId="S::pvhja1@novartis.net::bb2d6fc5-c67c-42b0-a39a-b1f2e1ee4d9c" providerId="AD"/>
-  <person displayName="Angelo, Christopher (Ext)" id="{0546590D-0F7F-4A09-BEC4-F7737625FC2D}" userId="S::ANGELCH2@novartis.net::345a3c0a-a32c-4d70-b63b-cb504b1e49c5" providerId="AD"/>
-  <person displayName="Arora, Kamal-1" id="{ECCCFD04-E026-4003-8D0B-5429F4402C3F}" userId="S::ARORAKA7@novartis.net::3d82822d-1cf7-44c4-9276-94ac755b2de0" providerId="AD"/>
-</personList>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3697,7 +3692,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="177">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="177">
   <r>
     <x v="0"/>
     <m/>
@@ -6265,9 +6260,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -6588,92 +6580,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H1" dT="2025-12-11T14:32:21.41" personId="{0B1E5331-89E5-4E56-B252-A4F43E545167}" id="{668AAA87-F2FF-4D96-AD0D-C9810EB8844F}">
-    <text>Demand/Forecast - comes from TACTPlan 
-Sunset:
-CPF, CRF, Automatrix, UTM matrix etc.</text>
-  </threadedComment>
-  <threadedComment ref="K11" dT="2025-10-23T13:02:42.92" personId="{ECCCFD04-E026-4003-8D0B-5429F4402C3F}" id="{94343ADA-C78E-4719-985D-40974469995F}">
-    <text>Discuss with Vivek</text>
-  </threadedComment>
-  <threadedComment ref="K15" dT="2025-10-24T12:55:52.23" personId="{E75BCEEB-DF11-46FF-B89C-3A408FA07791}" id="{349B11BE-9766-4493-9709-CB297EFCE6AA}">
-    <text>Javid: 
-@Arora, Kamal-1 
-Model based: Utilize predictive analytics and machine learning to automate the next best action (message), best channel and ideal timing for audience segments.
-Ad Hoc: Targeted one-off email sends triggered by specific needs or event/ webinar reminders
-Cadenced: Scheduled emails at pre-defined intervals to consistently educate, engage and influence customer behavior over time
-Real-time: Automate instant context aware emails that responds directly to user actions, ensuring timely and highly relevant engagement
-Real-time &amp; Cadenced: Immediate behavior driven email then continue to nurture through a structured sequence of emails designed to guide the users towards next best outcomes.</text>
-    <mentions>
-      <mention mentionpersonId="{74FF87B2-1D80-4853-9B2F-A6139ADF2B26}" mentionId="{3C646596-35CB-411F-8FBE-6BCBD464BB44}" startIndex="8" length="15"/>
-    </mentions>
-  </threadedComment>
-  <threadedComment ref="E123" dT="2025-11-17T15:33:53.41" personId="{0B1E5331-89E5-4E56-B252-A4F43E545167}" id="{E28A2662-9AB5-4B23-B3D4-E268D3C609C9}">
-    <text>https://novartisdevelop.atlassian.net/wiki/spaces/NMA/pages/209019961348/DISCOVERY+KISQALI+Lapsed+Writer+Journey</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>1740439423</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="112" url="https://novartisdevelop.atlassian.net/wiki/spaces/NMA/pages/209019961348/DISCOVERY+KISQALI+Lapsed+Writer+Journey"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B1" dT="2025-11-21T16:01:26.37" personId="{0B1E5331-89E5-4E56-B252-A4F43E545167}" id="{AD5A7C7D-8501-46FC-A6D5-E09485CA48E5}">
-    <text>Vijaywargiya, Nikita (Ext) to provide the following information from Morajkar, Hemant (Ext)
-1 ) The Attributes details under all the Metadata Objects for the different Campaign types
-2) Screen shot of CMA tool with the information need to generate the Campaign Code
-This will help to close the required information needed for OMS to have generate Campaign Code</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="G9" dT="2025-10-23T13:02:42.92" personId="{ECCCFD04-E026-4003-8D0B-5429F4402C3F}" id="{D94DFA96-0661-4B5C-A2DC-03ACCF1F194B}">
-    <text>Discuss with Vivek</text>
-  </threadedComment>
-  <threadedComment ref="G13" dT="2025-10-24T12:55:52.23" personId="{E75BCEEB-DF11-46FF-B89C-3A408FA07791}" id="{1A6CE08A-8E87-4150-AC3E-567781FC2317}">
-    <text>Javid: 
-@Arora, Kamal-1 
-Model based: Utilize predictive analytics and machine learning to automate the next best action (message), best channel and ideal timing for audience segments.
-Ad Hoc: Targeted one-off email sends triggered by specific needs or event/ webinar reminders
-Cadenced: Scheduled emails at pre-defined intervals to consistently educate, engage and influence customer behavior over time
-Real-time: Automate instant context aware emails that responds directly to user actions, ensuring timely and highly relevant engagement
-Real-time &amp; Cadenced: Immediate behavior driven email then continue to nurture through a structured sequence of emails designed to guide the users towards next best outcomes.</text>
-    <mentions>
-      <mention mentionpersonId="{74FF87B2-1D80-4853-9B2F-A6139ADF2B26}" mentionId="{C38C610C-4748-434C-8DFE-3331FB526F46}" startIndex="8" length="15"/>
-    </mentions>
-  </threadedComment>
-  <threadedComment ref="A14" dT="2025-08-06T11:15:40.62" personId="{640FEB8E-85D3-4E0D-B758-FCE42ED412AC}" id="{59FC6082-78B3-44E6-8212-B4D830E2C221}">
-    <text>Need to figureout one single proofing list per campaign. If one pool list then it will be same for all the emails under the campaigns and also for the Litmus and Segmentation</text>
-  </threadedComment>
-  <threadedComment ref="A19" dT="2025-11-21T16:01:26.37" personId="{0B1E5331-89E5-4E56-B252-A4F43E545167}" id="{04581291-9470-4CFF-ACE3-9839095591DA}">
-    <text>Vijaywargiya, Nikita (Ext) to provide the following information from Morajkar, Hemant (Ext)
-1 ) The Attributes details under all the Metadata Objects for the different Campaign types
-2) Screen shot of CMA tool with the information need to generate the Campaign Code
-This will help to close the required information needed for OMS to have generate Campaign Code</text>
-  </threadedComment>
-  <threadedComment ref="B88" dT="2025-11-07T15:39:27.34" personId="{0546590D-0F7F-4A09-BEC4-F7737625FC2D}" id="{67CAACE6-FA8C-4948-AE1A-B1133E759D77}">
-    <text>Line item 64 to 73 have been added in</text>
-  </threadedComment>
-  <threadedComment ref="B154" dT="2025-11-17T15:33:53.41" personId="{0B1E5331-89E5-4E56-B252-A4F43E545167}" id="{B46239CA-7BB6-4D64-A842-515993D28EAD}">
-    <text>https://novartisdevelop.atlassian.net/wiki/spaces/NMA/pages/209019961348/DISCOVERY+KISQALI+Lapsed+Writer+Journey</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>1740439423</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="112" url="https://novartisdevelop.atlassian.net/wiki/spaces/NMA/pages/209019961348/DISCOVERY+KISQALI+Lapsed+Writer+Journey"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L178"/>
@@ -6689,7 +6595,7 @@
     <col min="8" max="8" width="34.54296875" style="2" customWidth="1"/>
     <col min="9" max="9" width="15.08984375" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.90625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="90.7265625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="36.54296875" style="2" customWidth="1"/>
     <col min="12" max="12" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6735,11 +6641,11 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="87" t="s">
+      <c r="B2" s="110"/>
+      <c r="C2" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E2" s="8" t="s">
@@ -6749,7 +6655,7 @@
       <c r="G2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="93" t="s">
+      <c r="H2" s="91" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="8" t="s">
@@ -6767,11 +6673,11 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="87" t="s">
+      <c r="B3" s="110"/>
+      <c r="C3" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E3" s="8" t="s">
@@ -6781,7 +6687,7 @@
       <c r="G3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="93" t="s">
+      <c r="H3" s="91" t="s">
         <v>478</v>
       </c>
       <c r="I3" s="8" t="s">
@@ -6799,11 +6705,11 @@
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="87" t="s">
+      <c r="B4" s="110"/>
+      <c r="C4" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D4" s="87" t="s">
+      <c r="D4" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -6813,7 +6719,7 @@
       <c r="G4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="93" t="s">
+      <c r="H4" s="91" t="s">
         <v>486</v>
       </c>
       <c r="I4" s="8" t="s">
@@ -6833,11 +6739,11 @@
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="87" t="s">
+      <c r="B5" s="110"/>
+      <c r="C5" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -6847,7 +6753,7 @@
       <c r="G5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="93" t="s">
+      <c r="H5" s="91" t="s">
         <v>477</v>
       </c>
       <c r="I5" s="8" t="s">
@@ -6867,11 +6773,11 @@
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="87" t="s">
+      <c r="B6" s="130"/>
+      <c r="C6" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D6" s="87" t="s">
+      <c r="D6" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -6881,7 +6787,7 @@
       <c r="G6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="93" t="s">
+      <c r="H6" s="91" t="s">
         <v>477</v>
       </c>
       <c r="I6" s="8" t="s">
@@ -6901,11 +6807,11 @@
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="87" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D7" s="87" t="s">
+      <c r="D7" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E7" s="8" t="s">
@@ -6915,7 +6821,7 @@
       <c r="G7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="93" t="s">
+      <c r="H7" s="91" t="s">
         <v>485</v>
       </c>
       <c r="I7" s="8" t="s">
@@ -6933,11 +6839,11 @@
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="87" t="s">
+      <c r="B8" s="110"/>
+      <c r="C8" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D8" s="87" t="s">
+      <c r="D8" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E8" s="14" t="s">
@@ -6949,7 +6855,7 @@
       <c r="G8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="93" t="s">
+      <c r="H8" s="91" t="s">
         <v>488</v>
       </c>
       <c r="I8" s="8" t="s">
@@ -6969,24 +6875,24 @@
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="87" t="s">
+      <c r="B9" s="110"/>
+      <c r="C9" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D9" s="87" t="s">
+      <c r="D9" s="85" t="s">
         <v>508</v>
       </c>
-      <c r="E9" s="85" t="s">
+      <c r="E9" s="83" t="s">
         <v>24</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="85" t="s">
+      <c r="H9" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="85"/>
+      <c r="I9" s="83"/>
       <c r="J9" s="8" t="s">
         <v>12</v>
       </c>
@@ -6995,15 +6901,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="100">
+    <row r="10" spans="1:12" ht="200">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="87" t="s">
+      <c r="B10" s="110"/>
+      <c r="C10" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D10" s="87" t="s">
+      <c r="D10" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E10" s="10" t="s">
@@ -7029,18 +6935,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="137.5">
+    <row r="11" spans="1:12" ht="187.5">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="87" t="s">
+      <c r="B11" s="110"/>
+      <c r="C11" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D11" s="87" t="s">
+      <c r="D11" s="85" t="s">
         <v>511</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="76" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="8" t="s">
@@ -7067,11 +6973,11 @@
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="87" t="s">
+      <c r="B12" s="110"/>
+      <c r="C12" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D12" s="87" t="s">
+      <c r="D12" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -7083,7 +6989,7 @@
       <c r="G12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="93" t="s">
+      <c r="H12" s="91" t="s">
         <v>487</v>
       </c>
       <c r="I12" s="8" t="s">
@@ -7103,24 +7009,24 @@
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="87" t="s">
+      <c r="B13" s="110"/>
+      <c r="C13" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D13" s="87" t="s">
+      <c r="D13" s="85" t="s">
         <v>511</v>
       </c>
-      <c r="E13" s="85" t="s">
+      <c r="E13" s="83" t="s">
         <v>38</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="86" t="s">
+      <c r="H13" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="85"/>
+      <c r="I13" s="83"/>
       <c r="J13" s="8" t="s">
         <v>12</v>
       </c>
@@ -7135,11 +7041,11 @@
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="87" t="s">
+      <c r="B14" s="110"/>
+      <c r="C14" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D14" s="87" t="s">
+      <c r="D14" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E14" s="8" t="s">
@@ -7161,15 +7067,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="37.5">
+    <row r="15" spans="1:12" ht="87.5">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="87" t="s">
+      <c r="B15" s="110"/>
+      <c r="C15" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D15" s="87"/>
+      <c r="D15" s="85"/>
       <c r="E15" s="16" t="s">
         <v>41</v>
       </c>
@@ -7197,11 +7103,11 @@
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="87" t="s">
+      <c r="B16" s="110"/>
+      <c r="C16" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D16" s="87" t="s">
+      <c r="D16" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -7230,10 +7136,10 @@
         <v>0</v>
       </c>
       <c r="B17" s="1"/>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D17" s="87" t="s">
+      <c r="D17" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E17" s="16" t="s">
@@ -7266,10 +7172,10 @@
         <v>0</v>
       </c>
       <c r="B18" s="1"/>
-      <c r="C18" s="87" t="s">
+      <c r="C18" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D18" s="87" t="s">
+      <c r="D18" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E18" s="16" t="s">
@@ -7298,10 +7204,10 @@
         <v>0</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D19" s="87" t="s">
+      <c r="D19" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E19" s="16" t="s">
@@ -7329,11 +7235,11 @@
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="87" t="s">
+      <c r="B20" s="110"/>
+      <c r="C20" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D20" s="87" t="s">
+      <c r="D20" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E20" s="16" t="s">
@@ -7361,33 +7267,35 @@
       <c r="A21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="87" t="s">
+      <c r="B21" s="111"/>
+      <c r="C21" s="111" t="s">
         <v>492</v>
       </c>
-      <c r="D21" s="87" t="s">
+      <c r="D21" s="111" t="s">
         <v>511</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="43"/>
-      <c r="L21" s="16" t="s">
+      <c r="K21" s="111" t="s">
+        <v>635</v>
+      </c>
+      <c r="L21" s="112" t="s">
         <v>57</v>
       </c>
     </row>
@@ -7395,14 +7303,14 @@
       <c r="A22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="87" t="s">
+      <c r="B22" s="110"/>
+      <c r="C22" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D22" s="87" t="s">
+      <c r="D22" s="85" t="s">
         <v>511</v>
       </c>
-      <c r="E22" s="84" t="s">
+      <c r="E22" s="82" t="s">
         <v>465</v>
       </c>
       <c r="F22" s="16"/>
@@ -7427,14 +7335,14 @@
       <c r="A23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="87" t="s">
+      <c r="B23" s="110"/>
+      <c r="C23" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D23" s="87" t="s">
+      <c r="D23" s="85" t="s">
         <v>511</v>
       </c>
-      <c r="E23" s="84" t="s">
+      <c r="E23" s="82" t="s">
         <v>464</v>
       </c>
       <c r="F23" s="16"/>
@@ -7459,11 +7367,11 @@
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="87" t="s">
+      <c r="B24" s="110"/>
+      <c r="C24" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D24" s="87" t="s">
+      <c r="D24" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E24" s="69" t="s">
@@ -7491,14 +7399,14 @@
       <c r="A25" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="87" t="s">
+      <c r="B25" s="110"/>
+      <c r="C25" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D25" s="87" t="s">
+      <c r="D25" s="85" t="s">
         <v>511</v>
       </c>
-      <c r="E25" s="84" t="s">
+      <c r="E25" s="82" t="s">
         <v>469</v>
       </c>
       <c r="F25" s="16"/>
@@ -7523,14 +7431,14 @@
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="87" t="s">
+      <c r="B26" s="110"/>
+      <c r="C26" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D26" s="87" t="s">
+      <c r="D26" s="85" t="s">
         <v>511</v>
       </c>
-      <c r="E26" s="84" t="s">
+      <c r="E26" s="82" t="s">
         <v>471</v>
       </c>
       <c r="F26" s="16" t="s">
@@ -7557,33 +7465,33 @@
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="87" t="s">
+      <c r="B27" s="111"/>
+      <c r="C27" s="111" t="s">
         <v>492</v>
       </c>
-      <c r="D27" s="87" t="s">
+      <c r="D27" s="111" t="s">
         <v>511</v>
       </c>
-      <c r="E27" s="84" t="s">
+      <c r="E27" s="115" t="s">
         <v>472</v>
       </c>
-      <c r="F27" s="83" t="s">
+      <c r="F27" s="116" t="s">
         <v>474</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="J27" s="16" t="s">
+      <c r="J27" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K27" s="43"/>
-      <c r="L27" s="16" t="s">
+      <c r="K27" s="111"/>
+      <c r="L27" s="112" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7591,33 +7499,33 @@
       <c r="A28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="87" t="s">
+      <c r="B28" s="111"/>
+      <c r="C28" s="111" t="s">
         <v>492</v>
       </c>
-      <c r="D28" s="87" t="s">
+      <c r="D28" s="111" t="s">
         <v>511</v>
       </c>
-      <c r="E28" s="84" t="s">
+      <c r="E28" s="115" t="s">
         <v>473</v>
       </c>
-      <c r="F28" s="83" t="s">
+      <c r="F28" s="116" t="s">
         <v>474</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="J28" s="16" t="s">
+      <c r="J28" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K28" s="43"/>
-      <c r="L28" s="16" t="s">
+      <c r="K28" s="111"/>
+      <c r="L28" s="112" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7626,10 +7534,10 @@
         <v>53</v>
       </c>
       <c r="B29" s="1"/>
-      <c r="C29" s="87" t="s">
+      <c r="C29" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D29" s="87" t="s">
+      <c r="D29" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E29" s="16" t="s">
@@ -7658,16 +7566,16 @@
         <v>53</v>
       </c>
       <c r="B30" s="1"/>
-      <c r="C30" s="87" t="s">
+      <c r="C30" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D30" s="87" t="s">
+      <c r="D30" s="85" t="s">
         <v>511</v>
       </c>
-      <c r="E30" s="84" t="s">
+      <c r="E30" s="82" t="s">
         <v>475</v>
       </c>
-      <c r="F30" s="83" t="s">
+      <c r="F30" s="81" t="s">
         <v>476</v>
       </c>
       <c r="G30" s="8" t="s">
@@ -7691,11 +7599,11 @@
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="82"/>
-      <c r="C31" s="87" t="s">
+      <c r="B31" s="80"/>
+      <c r="C31" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D31" s="87" t="s">
+      <c r="D31" s="85" t="s">
         <v>513</v>
       </c>
       <c r="E31" s="16" t="s">
@@ -7725,33 +7633,35 @@
       <c r="A32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="82"/>
-      <c r="C32" s="87" t="s">
+      <c r="B32" s="117"/>
+      <c r="C32" s="44" t="s">
         <v>492</v>
       </c>
-      <c r="D32" s="87" t="s">
+      <c r="D32" s="44" t="s">
         <v>511</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="J32" s="16" t="s">
+      <c r="J32" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="K32" s="43"/>
-      <c r="L32" s="16" t="s">
+      <c r="K32" s="44" t="s">
+        <v>619</v>
+      </c>
+      <c r="L32" s="61" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7759,11 +7669,11 @@
       <c r="A33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="82"/>
-      <c r="C33" s="87" t="s">
+      <c r="B33" s="118"/>
+      <c r="C33" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D33" s="87" t="s">
+      <c r="D33" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E33" s="16" t="s">
@@ -7791,11 +7701,11 @@
       <c r="A34" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="82"/>
-      <c r="C34" s="87" t="s">
+      <c r="B34" s="80"/>
+      <c r="C34" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D34" s="87" t="s">
+      <c r="D34" s="85" t="s">
         <v>512</v>
       </c>
       <c r="E34" s="16" t="s">
@@ -7823,13 +7733,13 @@
       <c r="A35" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="87" t="s">
+      <c r="C35" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D35" s="87" t="s">
+      <c r="D35" s="85" t="s">
         <v>512</v>
       </c>
       <c r="E35" s="16" t="s">
@@ -7859,13 +7769,13 @@
       <c r="A36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="82" t="s">
+      <c r="B36" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="87" t="s">
+      <c r="C36" s="85" t="s">
         <v>493</v>
       </c>
-      <c r="D36" s="87" t="s">
+      <c r="D36" s="85" t="s">
         <v>512</v>
       </c>
       <c r="E36" s="16" t="s">
@@ -7895,13 +7805,13 @@
       <c r="A37" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="82" t="s">
+      <c r="B37" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="87" t="s">
+      <c r="C37" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D37" s="87" t="s">
+      <c r="D37" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E37" s="16" t="s">
@@ -7931,13 +7841,13 @@
       <c r="A38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="82" t="s">
+      <c r="B38" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="87" t="s">
+      <c r="C38" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D38" s="87" t="s">
+      <c r="D38" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E38" s="16" t="s">
@@ -7967,13 +7877,13 @@
       <c r="A39" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="82" t="s">
+      <c r="B39" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="87" t="s">
+      <c r="C39" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D39" s="87" t="s">
+      <c r="D39" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E39" s="16" t="s">
@@ -8003,13 +7913,13 @@
       <c r="A40" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="82" t="s">
+      <c r="B40" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="87" t="s">
+      <c r="C40" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D40" s="87" t="s">
+      <c r="D40" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E40" s="16" t="s">
@@ -8039,13 +7949,13 @@
       <c r="A41" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B41" s="82" t="s">
+      <c r="B41" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="87" t="s">
+      <c r="C41" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D41" s="87" t="s">
+      <c r="D41" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E41" s="16" t="s">
@@ -8075,35 +7985,35 @@
       <c r="A42" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="82" t="s">
+      <c r="B42" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="87" t="s">
+      <c r="C42" s="111" t="s">
         <v>492</v>
       </c>
-      <c r="D42" s="87" t="s">
+      <c r="D42" s="111" t="s">
         <v>511</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="112" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H42" s="16" t="s">
+      <c r="H42" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="I42" s="16" t="s">
+      <c r="I42" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="J42" s="16" t="s">
+      <c r="J42" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K42" s="43"/>
-      <c r="L42" s="16" t="s">
+      <c r="K42" s="111"/>
+      <c r="L42" s="112" t="s">
         <v>57</v>
       </c>
     </row>
@@ -8111,35 +8021,37 @@
       <c r="A43" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="82" t="s">
+      <c r="B43" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="C43" s="87" t="s">
+      <c r="C43" s="111" t="s">
         <v>492</v>
       </c>
-      <c r="D43" s="87" t="s">
+      <c r="D43" s="111" t="s">
         <v>511</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="112" t="s">
         <v>89</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="H43" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="I43" s="16" t="s">
+      <c r="I43" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="J43" s="16" t="s">
+      <c r="J43" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K43" s="43"/>
-      <c r="L43" s="16" t="s">
+      <c r="K43" s="111" t="s">
+        <v>620</v>
+      </c>
+      <c r="L43" s="112" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8147,13 +8059,13 @@
       <c r="A44" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="87" t="s">
+      <c r="C44" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D44" s="87" t="s">
+      <c r="D44" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E44" s="16" t="s">
@@ -8183,13 +8095,13 @@
       <c r="A45" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="82" t="s">
+      <c r="B45" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="87" t="s">
+      <c r="C45" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D45" s="87" t="s">
+      <c r="D45" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E45" s="16" t="s">
@@ -8219,13 +8131,13 @@
       <c r="A46" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B46" s="82" t="s">
+      <c r="B46" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="87" t="s">
+      <c r="C46" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D46" s="87" t="s">
+      <c r="D46" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E46" s="16" t="s">
@@ -8255,13 +8167,13 @@
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="82" t="s">
+      <c r="B47" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="87" t="s">
+      <c r="C47" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D47" s="87" t="s">
+      <c r="D47" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E47" s="16" t="s">
@@ -8291,13 +8203,13 @@
       <c r="A48" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B48" s="82" t="s">
+      <c r="B48" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="87" t="s">
+      <c r="C48" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D48" s="87" t="s">
+      <c r="D48" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E48" s="16" t="s">
@@ -8327,13 +8239,13 @@
       <c r="A49" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="82" t="s">
+      <c r="B49" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="87" t="s">
+      <c r="C49" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D49" s="87" t="s">
+      <c r="D49" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E49" s="16" t="s">
@@ -8363,13 +8275,13 @@
       <c r="A50" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B50" s="82" t="s">
+      <c r="B50" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C50" s="87" t="s">
+      <c r="C50" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D50" s="87" t="s">
+      <c r="D50" s="85" t="s">
         <v>511</v>
       </c>
       <c r="E50" s="16" t="s">
@@ -8399,11 +8311,11 @@
       <c r="A51" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B51" s="73"/>
-      <c r="C51" s="87" t="s">
+      <c r="B51" s="110"/>
+      <c r="C51" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D51" s="87" t="s">
+      <c r="D51" s="85" t="s">
         <v>509</v>
       </c>
       <c r="E51" s="8" t="s">
@@ -8434,10 +8346,10 @@
         <v>94</v>
       </c>
       <c r="B52" s="73"/>
-      <c r="C52" s="87" t="s">
+      <c r="C52" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D52" s="87"/>
+      <c r="D52" s="85"/>
       <c r="E52" s="16"/>
       <c r="F52" s="10" t="s">
         <v>97</v>
@@ -8455,11 +8367,11 @@
       <c r="A53" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B53" s="73"/>
-      <c r="C53" s="87" t="s">
+      <c r="B53" s="110"/>
+      <c r="C53" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D53" s="87" t="s">
+      <c r="D53" s="85" t="s">
         <v>509</v>
       </c>
       <c r="E53" s="10" t="s">
@@ -8489,11 +8401,11 @@
       <c r="A54" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="73"/>
-      <c r="C54" s="87" t="s">
+      <c r="B54" s="110"/>
+      <c r="C54" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D54" s="87" t="s">
+      <c r="D54" s="85" t="s">
         <v>509</v>
       </c>
       <c r="E54" s="10" t="s">
@@ -8523,11 +8435,11 @@
       <c r="A55" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B55" s="73"/>
-      <c r="C55" s="87" t="s">
+      <c r="B55" s="110"/>
+      <c r="C55" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D55" s="87" t="s">
+      <c r="D55" s="85" t="s">
         <v>509</v>
       </c>
       <c r="E55" s="10" t="s">
@@ -8558,10 +8470,10 @@
         <v>94</v>
       </c>
       <c r="B56" s="73"/>
-      <c r="C56" s="87" t="s">
+      <c r="C56" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D56" s="87" t="s">
+      <c r="D56" s="85" t="s">
         <v>500</v>
       </c>
       <c r="E56" s="8" t="s">
@@ -8591,14 +8503,14 @@
       <c r="A57" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B57" s="73" t="s">
+      <c r="B57" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="87" t="s">
+      <c r="C57" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D57" s="87"/>
-      <c r="E57" s="104" t="s">
+      <c r="D57" s="85"/>
+      <c r="E57" s="102" t="s">
         <v>105</v>
       </c>
       <c r="F57" s="43" t="s">
@@ -8619,14 +8531,14 @@
       <c r="A58" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B58" s="73" t="s">
+      <c r="B58" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="C58" s="87" t="s">
+      <c r="C58" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D58" s="87"/>
-      <c r="E58" s="105" t="s">
+      <c r="D58" s="85"/>
+      <c r="E58" s="103" t="s">
         <v>496</v>
       </c>
       <c r="F58" s="74" t="s">
@@ -8647,14 +8559,14 @@
       <c r="A59" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B59" s="73"/>
-      <c r="C59" s="87" t="s">
+      <c r="B59" s="110"/>
+      <c r="C59" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D59" s="87" t="s">
+      <c r="D59" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E59" s="84" t="s">
+      <c r="E59" s="82" t="s">
         <v>110</v>
       </c>
       <c r="F59" s="10" t="s">
@@ -8681,14 +8593,14 @@
       <c r="A60" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="73"/>
-      <c r="C60" s="87" t="s">
+      <c r="B60" s="110"/>
+      <c r="C60" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D60" s="87" t="s">
+      <c r="D60" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E60" s="84" t="s">
+      <c r="E60" s="82" t="s">
         <v>15</v>
       </c>
       <c r="F60" s="10" t="s">
@@ -8715,14 +8627,14 @@
       <c r="A61" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="87" t="s">
+      <c r="B61" s="110"/>
+      <c r="C61" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D61" s="87" t="s">
+      <c r="D61" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E61" s="84" t="s">
+      <c r="E61" s="82" t="s">
         <v>111</v>
       </c>
       <c r="F61" s="10" t="s">
@@ -8749,14 +8661,14 @@
       <c r="A62" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B62" s="73"/>
-      <c r="C62" s="87" t="s">
+      <c r="B62" s="110"/>
+      <c r="C62" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D62" s="87" t="s">
+      <c r="D62" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E62" s="84" t="s">
+      <c r="E62" s="82" t="s">
         <v>112</v>
       </c>
       <c r="F62" s="10" t="s">
@@ -8783,14 +8695,14 @@
       <c r="A63" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B63" s="73"/>
-      <c r="C63" s="87" t="s">
+      <c r="B63" s="110"/>
+      <c r="C63" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D63" s="87" t="s">
+      <c r="D63" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E63" s="84" t="s">
+      <c r="E63" s="82" t="s">
         <v>44</v>
       </c>
       <c r="F63" s="10" t="s">
@@ -8817,14 +8729,14 @@
       <c r="A64" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="87" t="s">
+      <c r="B64" s="110"/>
+      <c r="C64" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D64" s="87" t="s">
+      <c r="D64" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E64" s="84" t="s">
+      <c r="E64" s="82" t="s">
         <v>113</v>
       </c>
       <c r="F64" s="10" t="s">
@@ -8851,14 +8763,14 @@
       <c r="A65" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="73"/>
-      <c r="C65" s="87" t="s">
+      <c r="B65" s="110"/>
+      <c r="C65" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D65" s="87" t="s">
+      <c r="D65" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E65" s="84" t="s">
+      <c r="E65" s="82" t="s">
         <v>114</v>
       </c>
       <c r="F65" s="10" t="s">
@@ -8885,14 +8797,14 @@
       <c r="A66" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B66" s="73"/>
-      <c r="C66" s="87" t="s">
+      <c r="B66" s="110"/>
+      <c r="C66" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D66" s="87" t="s">
+      <c r="D66" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E66" s="84" t="s">
+      <c r="E66" s="82" t="s">
         <v>115</v>
       </c>
       <c r="F66" s="10" t="s">
@@ -8919,14 +8831,14 @@
       <c r="A67" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="73"/>
-      <c r="C67" s="87" t="s">
+      <c r="B67" s="110"/>
+      <c r="C67" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="D67" s="87" t="s">
+      <c r="D67" s="85" t="s">
         <v>509</v>
       </c>
-      <c r="E67" s="84" t="s">
+      <c r="E67" s="82" t="s">
         <v>116</v>
       </c>
       <c r="F67" s="10" t="s">
@@ -8953,11 +8865,11 @@
       <c r="A68" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B68" s="73"/>
-      <c r="C68" s="87" t="s">
+      <c r="B68" s="110"/>
+      <c r="C68" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D68" s="87" t="s">
+      <c r="D68" s="85" t="s">
         <v>505</v>
       </c>
       <c r="E68" s="16" t="s">
@@ -8987,33 +8899,35 @@
       <c r="A69" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="87" t="s">
+      <c r="B69" s="111"/>
+      <c r="C69" s="111" t="s">
         <v>492</v>
       </c>
-      <c r="D69" s="87" t="s">
+      <c r="D69" s="111" t="s">
         <v>505</v>
       </c>
-      <c r="E69" s="16" t="s">
+      <c r="E69" s="112" t="s">
         <v>121</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" s="114" t="s">
         <v>503</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="H69" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="I69" s="16" t="s">
+      <c r="I69" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="J69" s="16" t="s">
+      <c r="J69" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="K69" s="43"/>
-      <c r="L69" s="16" t="s">
+      <c r="K69" s="111" t="s">
+        <v>627</v>
+      </c>
+      <c r="L69" s="112" t="s">
         <v>52</v>
       </c>
     </row>
@@ -9021,31 +8935,33 @@
       <c r="A70" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B70" s="73"/>
-      <c r="C70" s="87" t="s">
+      <c r="B70" s="111"/>
+      <c r="C70" s="111" t="s">
         <v>492</v>
       </c>
-      <c r="D70" s="87" t="s">
+      <c r="D70" s="111" t="s">
         <v>504</v>
       </c>
-      <c r="E70" s="16" t="s">
+      <c r="E70" s="112" t="s">
         <v>122</v>
       </c>
-      <c r="F70" s="16"/>
-      <c r="G70" s="8" t="s">
+      <c r="F70" s="112"/>
+      <c r="G70" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H70" s="8" t="s">
+      <c r="H70" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="I70" s="16" t="s">
+      <c r="I70" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="J70" s="16" t="s">
+      <c r="J70" s="112" t="s">
         <v>325</v>
       </c>
-      <c r="K70" s="43"/>
-      <c r="L70" s="16" t="s">
+      <c r="K70" s="111" t="s">
+        <v>628</v>
+      </c>
+      <c r="L70" s="112" t="s">
         <v>52</v>
       </c>
     </row>
@@ -9053,31 +8969,33 @@
       <c r="A71" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B71" s="73"/>
-      <c r="C71" s="87" t="s">
+      <c r="B71" s="44"/>
+      <c r="C71" s="44" t="s">
         <v>492</v>
       </c>
-      <c r="D71" s="87" t="s">
+      <c r="D71" s="44" t="s">
         <v>504</v>
       </c>
-      <c r="E71" s="16" t="s">
+      <c r="E71" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="F71" s="16"/>
-      <c r="G71" s="8" t="s">
+      <c r="F71" s="61"/>
+      <c r="G71" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="H71" s="8" t="s">
+      <c r="H71" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="I71" s="16" t="s">
+      <c r="I71" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="J71" s="16" t="s">
+      <c r="J71" s="61" t="s">
         <v>325</v>
       </c>
-      <c r="K71" s="43"/>
-      <c r="L71" s="16" t="s">
+      <c r="K71" s="44" t="s">
+        <v>629</v>
+      </c>
+      <c r="L71" s="61" t="s">
         <v>125</v>
       </c>
     </row>
@@ -9085,31 +9003,33 @@
       <c r="A72" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="87" t="s">
+      <c r="B72" s="44"/>
+      <c r="C72" s="44" t="s">
         <v>492</v>
       </c>
-      <c r="D72" s="87" t="s">
+      <c r="D72" s="44" t="s">
         <v>505</v>
       </c>
-      <c r="E72" s="16" t="s">
+      <c r="E72" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="F72" s="16"/>
-      <c r="G72" s="8" t="s">
+      <c r="F72" s="61"/>
+      <c r="G72" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="H72" s="8" t="s">
+      <c r="H72" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="I72" s="16" t="s">
+      <c r="I72" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="J72" s="16" t="s">
+      <c r="J72" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="K72" s="43"/>
-      <c r="L72" s="16" t="s">
+      <c r="K72" s="44" t="s">
+        <v>636</v>
+      </c>
+      <c r="L72" s="61" t="s">
         <v>57</v>
       </c>
     </row>
@@ -9118,13 +9038,13 @@
         <v>127</v>
       </c>
       <c r="B73" s="73"/>
-      <c r="C73" s="87"/>
-      <c r="D73" s="87"/>
+      <c r="C73" s="85"/>
+      <c r="D73" s="85"/>
       <c r="E73" s="8" t="s">
         <v>128</v>
       </c>
       <c r="F73" s="43"/>
-      <c r="G73" s="79" t="s">
+      <c r="G73" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H73" s="43"/>
@@ -9138,15 +9058,15 @@
         <v>127</v>
       </c>
       <c r="B74" s="73"/>
-      <c r="C74" s="87"/>
-      <c r="D74" s="87"/>
+      <c r="C74" s="85"/>
+      <c r="D74" s="85"/>
       <c r="E74" s="43" t="s">
         <v>129</v>
       </c>
       <c r="F74" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="G74" s="79" t="s">
+      <c r="G74" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H74" s="13"/>
@@ -9159,418 +9079,418 @@
       <c r="A75" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B75" s="73"/>
-      <c r="C75" s="87"/>
-      <c r="D75" s="87"/>
-      <c r="E75" s="106" t="s">
+      <c r="B75" s="44"/>
+      <c r="C75" s="44"/>
+      <c r="D75" s="44"/>
+      <c r="E75" s="124" t="s">
         <v>131</v>
       </c>
-      <c r="F75" s="16"/>
-      <c r="G75" s="79" t="s">
+      <c r="F75" s="61"/>
+      <c r="G75" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H75" s="16"/>
-      <c r="I75" s="16"/>
-      <c r="J75" s="43"/>
-      <c r="K75" s="43"/>
-      <c r="L75" s="16"/>
+      <c r="H75" s="61"/>
+      <c r="I75" s="61"/>
+      <c r="J75" s="44"/>
+      <c r="K75" s="44"/>
+      <c r="L75" s="61"/>
     </row>
     <row r="76" spans="1:12" s="72" customFormat="1" ht="70">
       <c r="A76" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B76" s="73"/>
-      <c r="C76" s="87"/>
-      <c r="D76" s="87"/>
-      <c r="E76" s="107" t="s">
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="F76" s="73"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="73"/>
-      <c r="J76" s="73"/>
-      <c r="K76" s="73"/>
-      <c r="L76" s="73"/>
+      <c r="F76" s="44"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44"/>
+      <c r="I76" s="44"/>
+      <c r="J76" s="44"/>
+      <c r="K76" s="44"/>
+      <c r="L76" s="44"/>
     </row>
     <row r="77" spans="1:12" ht="70">
       <c r="A77" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B77" s="73" t="s">
+      <c r="B77" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C77" s="87"/>
-      <c r="D77" s="87"/>
-      <c r="E77" s="106" t="s">
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="124" t="s">
         <v>132</v>
       </c>
-      <c r="F77" s="16"/>
-      <c r="G77" s="79" t="s">
+      <c r="F77" s="61"/>
+      <c r="G77" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H77" s="16"/>
-      <c r="I77" s="16"/>
-      <c r="J77" s="43"/>
-      <c r="K77" s="43"/>
-      <c r="L77" s="16"/>
+      <c r="H77" s="61"/>
+      <c r="I77" s="61"/>
+      <c r="J77" s="44"/>
+      <c r="K77" s="44"/>
+      <c r="L77" s="61"/>
     </row>
     <row r="78" spans="1:12" ht="70">
       <c r="A78" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B78" s="73" t="s">
+      <c r="B78" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C78" s="87"/>
-      <c r="D78" s="87"/>
-      <c r="E78" s="106" t="s">
+      <c r="C78" s="44"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="124" t="s">
         <v>133</v>
       </c>
-      <c r="F78" s="16"/>
-      <c r="G78" s="79" t="s">
+      <c r="F78" s="61"/>
+      <c r="G78" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H78" s="16"/>
-      <c r="I78" s="16"/>
-      <c r="J78" s="43"/>
-      <c r="K78" s="43"/>
-      <c r="L78" s="16"/>
+      <c r="H78" s="61"/>
+      <c r="I78" s="61"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="44"/>
+      <c r="L78" s="61"/>
     </row>
     <row r="79" spans="1:12" ht="70">
       <c r="A79" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B79" s="73" t="s">
+      <c r="B79" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C79" s="87"/>
-      <c r="D79" s="87"/>
-      <c r="E79" s="106" t="s">
+      <c r="C79" s="44"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="124" t="s">
         <v>134</v>
       </c>
-      <c r="F79" s="8"/>
-      <c r="G79" s="79" t="s">
+      <c r="F79" s="83"/>
+      <c r="G79" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="43"/>
-      <c r="L79" s="16"/>
+      <c r="H79" s="83"/>
+      <c r="I79" s="83"/>
+      <c r="J79" s="83"/>
+      <c r="K79" s="44"/>
+      <c r="L79" s="61"/>
     </row>
     <row r="80" spans="1:12" ht="70">
       <c r="A80" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B80" s="73" t="s">
+      <c r="B80" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C80" s="87"/>
-      <c r="D80" s="87"/>
-      <c r="E80" s="106" t="s">
+      <c r="C80" s="44"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="124" t="s">
         <v>135</v>
       </c>
-      <c r="F80" s="8"/>
-      <c r="G80" s="79" t="s">
+      <c r="F80" s="83"/>
+      <c r="G80" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="43"/>
-      <c r="L80" s="16"/>
+      <c r="H80" s="83"/>
+      <c r="I80" s="83"/>
+      <c r="J80" s="83"/>
+      <c r="K80" s="44"/>
+      <c r="L80" s="61"/>
     </row>
     <row r="81" spans="1:12" ht="70">
       <c r="A81" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B81" s="73" t="s">
+      <c r="B81" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C81" s="87"/>
-      <c r="D81" s="87"/>
-      <c r="E81" s="106" t="s">
+      <c r="C81" s="44"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="124" t="s">
         <v>136</v>
       </c>
-      <c r="F81" s="16" t="s">
+      <c r="F81" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="G81" s="79" t="s">
+      <c r="G81" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H81" s="16"/>
-      <c r="I81" s="16"/>
-      <c r="J81" s="43"/>
-      <c r="K81" s="43"/>
-      <c r="L81" s="16"/>
+      <c r="H81" s="61"/>
+      <c r="I81" s="61"/>
+      <c r="J81" s="44"/>
+      <c r="K81" s="44"/>
+      <c r="L81" s="61"/>
     </row>
     <row r="82" spans="1:12" ht="70">
       <c r="A82" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B82" s="73" t="s">
+      <c r="B82" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C82" s="87"/>
-      <c r="D82" s="87"/>
-      <c r="E82" s="106" t="s">
+      <c r="C82" s="44"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="124" t="s">
         <v>137</v>
       </c>
-      <c r="F82" s="16" t="s">
+      <c r="F82" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="G82" s="79" t="s">
+      <c r="G82" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H82" s="16"/>
-      <c r="I82" s="16"/>
-      <c r="J82" s="43"/>
-      <c r="K82" s="43"/>
-      <c r="L82" s="16"/>
+      <c r="H82" s="61"/>
+      <c r="I82" s="61"/>
+      <c r="J82" s="44"/>
+      <c r="K82" s="44"/>
+      <c r="L82" s="61"/>
     </row>
     <row r="83" spans="1:12" ht="70">
       <c r="A83" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B83" s="73" t="s">
+      <c r="B83" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C83" s="87"/>
-      <c r="D83" s="87"/>
-      <c r="E83" s="106" t="s">
+      <c r="C83" s="44"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="124" t="s">
         <v>139</v>
       </c>
-      <c r="F83" s="16" t="s">
+      <c r="F83" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="G83" s="79" t="s">
+      <c r="G83" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H83" s="16"/>
-      <c r="I83" s="16"/>
-      <c r="J83" s="43"/>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="61"/>
+      <c r="J83" s="44"/>
+      <c r="K83" s="61"/>
+      <c r="L83" s="61"/>
     </row>
     <row r="84" spans="1:12" ht="70">
       <c r="A84" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B84" s="73" t="s">
+      <c r="B84" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C84" s="87"/>
-      <c r="D84" s="87"/>
-      <c r="E84" s="106" t="s">
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="124" t="s">
         <v>140</v>
       </c>
-      <c r="F84" s="16"/>
-      <c r="G84" s="79" t="s">
+      <c r="F84" s="61"/>
+      <c r="G84" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H84" s="16"/>
-      <c r="I84" s="16"/>
-      <c r="J84" s="43"/>
-      <c r="K84" s="43"/>
-      <c r="L84" s="16"/>
+      <c r="H84" s="61"/>
+      <c r="I84" s="61"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="44"/>
+      <c r="L84" s="61"/>
     </row>
     <row r="85" spans="1:12" ht="70">
       <c r="A85" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B85" s="73" t="s">
+      <c r="B85" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C85" s="87"/>
-      <c r="D85" s="87"/>
-      <c r="E85" s="106" t="s">
+      <c r="C85" s="44"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="124" t="s">
         <v>141</v>
       </c>
-      <c r="F85" s="13" t="s">
+      <c r="F85" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="G85" s="79" t="s">
+      <c r="G85" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="43"/>
-      <c r="K85" s="43"/>
-      <c r="L85" s="16"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="18"/>
+      <c r="J85" s="44"/>
+      <c r="K85" s="44"/>
+      <c r="L85" s="61"/>
     </row>
     <row r="86" spans="1:12" ht="70">
       <c r="A86" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B86" s="73" t="s">
+      <c r="B86" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C86" s="87"/>
-      <c r="D86" s="87"/>
-      <c r="E86" s="106" t="s">
+      <c r="C86" s="44"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="124" t="s">
         <v>143</v>
       </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="79" t="s">
+      <c r="F86" s="61"/>
+      <c r="G86" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H86" s="16"/>
-      <c r="I86" s="16"/>
-      <c r="J86" s="43"/>
-      <c r="K86" s="43"/>
-      <c r="L86" s="16"/>
+      <c r="H86" s="61"/>
+      <c r="I86" s="61"/>
+      <c r="J86" s="44"/>
+      <c r="K86" s="44"/>
+      <c r="L86" s="61"/>
     </row>
     <row r="87" spans="1:12" ht="70">
       <c r="A87" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B87" s="73" t="s">
+      <c r="B87" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C87" s="87"/>
-      <c r="D87" s="87"/>
-      <c r="E87" s="106" t="s">
+      <c r="C87" s="44"/>
+      <c r="D87" s="44"/>
+      <c r="E87" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="F87" s="13" t="s">
+      <c r="F87" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="G87" s="79" t="s">
+      <c r="G87" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
-      <c r="J87" s="43"/>
-      <c r="K87" s="43"/>
-      <c r="L87" s="16"/>
+      <c r="H87" s="18"/>
+      <c r="I87" s="18"/>
+      <c r="J87" s="44"/>
+      <c r="K87" s="44"/>
+      <c r="L87" s="61"/>
     </row>
     <row r="88" spans="1:12" ht="70">
       <c r="A88" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B88" s="73" t="s">
+      <c r="B88" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C88" s="87"/>
-      <c r="D88" s="87"/>
-      <c r="E88" s="106" t="s">
+      <c r="C88" s="44"/>
+      <c r="D88" s="44"/>
+      <c r="E88" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="F88" s="16"/>
-      <c r="G88" s="79" t="s">
+      <c r="F88" s="61"/>
+      <c r="G88" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H88" s="16"/>
-      <c r="I88" s="16"/>
-      <c r="J88" s="43"/>
-      <c r="K88" s="45"/>
-      <c r="L88" s="16"/>
+      <c r="H88" s="61"/>
+      <c r="I88" s="61"/>
+      <c r="J88" s="44"/>
+      <c r="K88" s="126"/>
+      <c r="L88" s="61"/>
     </row>
     <row r="89" spans="1:12" ht="70">
       <c r="A89" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B89" s="73" t="s">
+      <c r="B89" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C89" s="87"/>
-      <c r="D89" s="87"/>
-      <c r="E89" s="106" t="s">
+      <c r="C89" s="44"/>
+      <c r="D89" s="44"/>
+      <c r="E89" s="124" t="s">
         <v>147</v>
       </c>
-      <c r="F89" s="16"/>
-      <c r="G89" s="79" t="s">
+      <c r="F89" s="61"/>
+      <c r="G89" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H89" s="16"/>
-      <c r="I89" s="16"/>
-      <c r="J89" s="43"/>
-      <c r="K89" s="45"/>
-      <c r="L89" s="16"/>
+      <c r="H89" s="61"/>
+      <c r="I89" s="61"/>
+      <c r="J89" s="44"/>
+      <c r="K89" s="126"/>
+      <c r="L89" s="61"/>
     </row>
     <row r="90" spans="1:12" ht="70">
       <c r="A90" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B90" s="73" t="s">
+      <c r="B90" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C90" s="87"/>
-      <c r="D90" s="87"/>
-      <c r="E90" s="106" t="s">
+      <c r="C90" s="44"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="124" t="s">
         <v>148</v>
       </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="79" t="s">
+      <c r="F90" s="61"/>
+      <c r="G90" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H90" s="16"/>
-      <c r="I90" s="16"/>
-      <c r="J90" s="43"/>
-      <c r="K90" s="43"/>
-      <c r="L90" s="16"/>
+      <c r="H90" s="61"/>
+      <c r="I90" s="61"/>
+      <c r="J90" s="44"/>
+      <c r="K90" s="44"/>
+      <c r="L90" s="61"/>
     </row>
     <row r="91" spans="1:12" ht="70">
       <c r="A91" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B91" s="73" t="s">
+      <c r="B91" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C91" s="87"/>
-      <c r="D91" s="87"/>
-      <c r="E91" s="108" t="s">
+      <c r="C91" s="44"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F91" s="16"/>
-      <c r="G91" s="79" t="s">
+      <c r="F91" s="61"/>
+      <c r="G91" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16"/>
-      <c r="J91" s="43"/>
-      <c r="K91" s="43"/>
-      <c r="L91" s="16"/>
+      <c r="H91" s="61"/>
+      <c r="I91" s="61"/>
+      <c r="J91" s="44"/>
+      <c r="K91" s="44"/>
+      <c r="L91" s="61"/>
     </row>
     <row r="92" spans="1:12" ht="70">
       <c r="A92" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B92" s="73"/>
-      <c r="C92" s="87"/>
-      <c r="D92" s="87"/>
-      <c r="E92" s="109" t="s">
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="128" t="s">
         <v>150</v>
       </c>
-      <c r="F92" s="15" t="s">
+      <c r="F92" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="G92" s="79" t="s">
+      <c r="G92" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="43" t="s">
+      <c r="H92" s="62"/>
+      <c r="I92" s="62"/>
+      <c r="J92" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="K92" s="43"/>
-      <c r="L92" s="16"/>
+      <c r="K92" s="44"/>
+      <c r="L92" s="61"/>
     </row>
     <row r="93" spans="1:12" ht="70">
       <c r="A93" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B93" s="73"/>
-      <c r="C93" s="87"/>
-      <c r="D93" s="87"/>
+      <c r="B93" s="44"/>
+      <c r="C93" s="85"/>
+      <c r="D93" s="85"/>
       <c r="E93" s="13" t="s">
         <v>153</v>
       </c>
       <c r="F93" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="G93" s="79" t="s">
+      <c r="G93" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H93" s="48"/>
@@ -9585,16 +9505,16 @@
       <c r="A94" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="73"/>
-      <c r="C94" s="87"/>
-      <c r="D94" s="87"/>
+      <c r="B94" s="44"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="13" t="s">
         <v>153</v>
       </c>
       <c r="F94" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="G94" s="79" t="s">
+      <c r="G94" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H94" s="48"/>
@@ -9609,16 +9529,16 @@
       <c r="A95" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="73"/>
-      <c r="C95" s="87"/>
-      <c r="D95" s="87"/>
+      <c r="B95" s="44"/>
+      <c r="C95" s="85"/>
+      <c r="D95" s="85"/>
       <c r="E95" s="13" t="s">
         <v>153</v>
       </c>
       <c r="F95" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="G95" s="79" t="s">
+      <c r="G95" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H95" s="48"/>
@@ -9633,16 +9553,16 @@
       <c r="A96" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B96" s="73"/>
-      <c r="C96" s="87"/>
-      <c r="D96" s="87"/>
+      <c r="B96" s="44"/>
+      <c r="C96" s="85"/>
+      <c r="D96" s="85"/>
       <c r="E96" s="13" t="s">
         <v>153</v>
       </c>
       <c r="F96" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="G96" s="79" t="s">
+      <c r="G96" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H96" s="48"/>
@@ -9657,12 +9577,12 @@
       <c r="A97" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B97" s="73"/>
-      <c r="C97" s="87"/>
-      <c r="D97" s="87"/>
-      <c r="E97" s="106"/>
+      <c r="B97" s="44"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
+      <c r="E97" s="104"/>
       <c r="F97" s="16"/>
-      <c r="G97" s="79" t="s">
+      <c r="G97" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H97" s="16"/>
@@ -9675,12 +9595,12 @@
       <c r="A98" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B98" s="73"/>
-      <c r="C98" s="87"/>
-      <c r="D98" s="87"/>
-      <c r="E98" s="106"/>
+      <c r="B98" s="44"/>
+      <c r="C98" s="85"/>
+      <c r="D98" s="85"/>
+      <c r="E98" s="104"/>
       <c r="F98" s="16"/>
-      <c r="G98" s="79" t="s">
+      <c r="G98" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H98" s="16"/>
@@ -9693,14 +9613,14 @@
       <c r="A99" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="87"/>
-      <c r="D99" s="87"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="85"/>
+      <c r="D99" s="85"/>
       <c r="E99" s="43" t="s">
         <v>156</v>
       </c>
       <c r="F99" s="43"/>
-      <c r="G99" s="79" t="s">
+      <c r="G99" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H99" s="43"/>
@@ -9713,14 +9633,14 @@
       <c r="A100" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B100" s="73"/>
-      <c r="C100" s="87"/>
-      <c r="D100" s="87"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="85"/>
+      <c r="D100" s="85"/>
       <c r="E100" s="43" t="s">
         <v>157</v>
       </c>
       <c r="F100" s="43"/>
-      <c r="G100" s="79" t="s">
+      <c r="G100" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H100" s="43"/>
@@ -9733,12 +9653,12 @@
       <c r="A101" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B101" s="73"/>
-      <c r="C101" s="87"/>
-      <c r="D101" s="87"/>
+      <c r="B101" s="44"/>
+      <c r="C101" s="85"/>
+      <c r="D101" s="85"/>
       <c r="E101" s="16"/>
       <c r="F101" s="16"/>
-      <c r="G101" s="79" t="s">
+      <c r="G101" s="77" t="s">
         <v>47</v>
       </c>
       <c r="H101" s="16"/>
@@ -9751,13 +9671,13 @@
       <c r="A102" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B102" s="110" t="s">
+      <c r="B102" s="66" t="s">
         <v>616</v>
       </c>
-      <c r="C102" s="111" t="s">
+      <c r="C102" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D102" s="87" t="s">
+      <c r="D102" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E102" s="16" t="s">
@@ -9785,13 +9705,13 @@
       <c r="A103" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B103" s="110" t="s">
+      <c r="B103" s="66" t="s">
         <v>616</v>
       </c>
-      <c r="C103" s="111" t="s">
+      <c r="C103" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D103" s="87" t="s">
+      <c r="D103" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E103" s="16" t="s">
@@ -9819,13 +9739,13 @@
       <c r="A104" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B104" s="110" t="s">
+      <c r="B104" s="66" t="s">
         <v>616</v>
       </c>
-      <c r="C104" s="111" t="s">
+      <c r="C104" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D104" s="87" t="s">
+      <c r="D104" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E104" s="16" t="s">
@@ -9853,13 +9773,13 @@
       <c r="A105" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B105" s="110" t="s">
+      <c r="B105" s="66" t="s">
         <v>616</v>
       </c>
-      <c r="C105" s="111" t="s">
+      <c r="C105" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D105" s="87" t="s">
+      <c r="D105" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E105" s="16" t="s">
@@ -9889,13 +9809,13 @@
       <c r="A106" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B106" s="110" t="s">
+      <c r="B106" s="66" t="s">
         <v>616</v>
       </c>
-      <c r="C106" s="111" t="s">
+      <c r="C106" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D106" s="87" t="s">
+      <c r="D106" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E106" s="16" t="s">
@@ -9923,13 +9843,13 @@
       <c r="A107" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B107" s="55" t="s">
+      <c r="B107" s="121" t="s">
         <v>170</v>
       </c>
-      <c r="C107" s="111" t="s">
+      <c r="C107" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D107" s="111"/>
+      <c r="D107" s="105"/>
       <c r="E107" s="55" t="s">
         <v>170</v>
       </c>
@@ -9945,13 +9865,13 @@
       <c r="A108" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B108" s="55" t="s">
+      <c r="B108" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="C108" s="111" t="s">
+      <c r="C108" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D108" s="87" t="s">
+      <c r="D108" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E108" s="16" t="s">
@@ -9968,20 +9888,22 @@
       <c r="J108" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="K108" s="16"/>
+      <c r="K108" s="16" t="s">
+        <v>630</v>
+      </c>
       <c r="L108" s="16"/>
     </row>
     <row r="109" spans="1:12" ht="65">
       <c r="A109" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B109" s="55" t="s">
+      <c r="B109" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="C109" s="111" t="s">
+      <c r="C109" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D109" s="87" t="s">
+      <c r="D109" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E109" s="16" t="s">
@@ -9998,20 +9920,22 @@
       <c r="J109" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="K109" s="16"/>
+      <c r="K109" s="16" t="s">
+        <v>630</v>
+      </c>
       <c r="L109" s="16"/>
     </row>
     <row r="110" spans="1:12" ht="65">
       <c r="A110" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B110" s="55" t="s">
+      <c r="B110" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="C110" s="111" t="s">
+      <c r="C110" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D110" s="87" t="s">
+      <c r="D110" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E110" s="16" t="s">
@@ -10028,20 +9952,22 @@
       <c r="J110" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="K110" s="16"/>
+      <c r="K110" s="16" t="s">
+        <v>630</v>
+      </c>
       <c r="L110" s="16"/>
     </row>
     <row r="111" spans="1:12" ht="65">
       <c r="A111" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B111" s="55" t="s">
+      <c r="B111" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="C111" s="111" t="s">
+      <c r="C111" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D111" s="87" t="s">
+      <c r="D111" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E111" s="16" t="s">
@@ -10058,20 +9984,22 @@
       <c r="J111" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="K111" s="16"/>
+      <c r="K111" s="16" t="s">
+        <v>630</v>
+      </c>
       <c r="L111" s="16"/>
     </row>
     <row r="112" spans="1:12" ht="65">
       <c r="A112" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B112" s="55" t="s">
+      <c r="B112" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="C112" s="111" t="s">
+      <c r="C112" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D112" s="87" t="s">
+      <c r="D112" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E112" s="16" t="s">
@@ -10088,20 +10016,22 @@
       <c r="J112" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="K112" s="16"/>
+      <c r="K112" s="16" t="s">
+        <v>630</v>
+      </c>
       <c r="L112" s="16"/>
     </row>
     <row r="113" spans="1:12" ht="65">
       <c r="A113" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B113" s="55" t="s">
+      <c r="B113" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="C113" s="111" t="s">
+      <c r="C113" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D113" s="87" t="s">
+      <c r="D113" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E113" s="16" t="s">
@@ -10118,20 +10048,22 @@
       <c r="J113" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="K113" s="16"/>
+      <c r="K113" s="16" t="s">
+        <v>631</v>
+      </c>
       <c r="L113" s="16"/>
     </row>
     <row r="114" spans="1:12" ht="65">
       <c r="A114" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B114" s="55" t="s">
+      <c r="B114" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="C114" s="111" t="s">
+      <c r="C114" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D114" s="87" t="s">
+      <c r="D114" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E114" s="16" t="s">
@@ -10148,20 +10080,22 @@
       <c r="J114" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="K114" s="16"/>
+      <c r="K114" s="16" t="s">
+        <v>631</v>
+      </c>
       <c r="L114" s="16"/>
     </row>
     <row r="115" spans="1:12" ht="65">
       <c r="A115" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B115" s="55" t="s">
+      <c r="B115" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="C115" s="111" t="s">
+      <c r="C115" s="105" t="s">
         <v>492</v>
       </c>
-      <c r="D115" s="87" t="s">
+      <c r="D115" s="85" t="s">
         <v>506</v>
       </c>
       <c r="E115" s="16" t="s">
@@ -10178,39 +10112,43 @@
       <c r="J115" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="K115" s="16"/>
+      <c r="K115" s="16" t="s">
+        <v>632</v>
+      </c>
       <c r="L115" s="16"/>
     </row>
     <row r="116" spans="1:12" ht="42">
       <c r="A116" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B116" s="110" t="s">
+      <c r="B116" s="122" t="s">
         <v>617</v>
       </c>
-      <c r="C116" s="111" t="s">
+      <c r="C116" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D116" s="87" t="s">
+      <c r="D116" s="111" t="s">
         <v>506</v>
       </c>
-      <c r="E116" s="16" t="s">
+      <c r="E116" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="F116" s="16"/>
-      <c r="G116" s="8" t="s">
+      <c r="F116" s="112"/>
+      <c r="G116" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H116" s="8" t="s">
+      <c r="H116" s="113" t="s">
         <v>161</v>
       </c>
-      <c r="I116" s="8" t="s">
+      <c r="I116" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="J116" s="16" t="s">
+      <c r="J116" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K116" s="16"/>
+      <c r="K116" s="112" t="s">
+        <v>633</v>
+      </c>
       <c r="L116" s="16" t="s">
         <v>13</v>
       </c>
@@ -10219,32 +10157,34 @@
       <c r="A117" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B117" s="110" t="s">
+      <c r="B117" s="122" t="s">
         <v>617</v>
       </c>
-      <c r="C117" s="111" t="s">
+      <c r="C117" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D117" s="87" t="s">
+      <c r="D117" s="111" t="s">
         <v>506</v>
       </c>
-      <c r="E117" s="16" t="s">
+      <c r="E117" s="112" t="s">
         <v>185</v>
       </c>
-      <c r="F117" s="16"/>
-      <c r="G117" s="8" t="s">
+      <c r="F117" s="112"/>
+      <c r="G117" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H117" s="8" t="s">
+      <c r="H117" s="113" t="s">
         <v>161</v>
       </c>
-      <c r="I117" s="8" t="s">
+      <c r="I117" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="J117" s="16" t="s">
+      <c r="J117" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K117" s="16"/>
+      <c r="K117" s="112" t="s">
+        <v>633</v>
+      </c>
       <c r="L117" s="16" t="s">
         <v>13</v>
       </c>
@@ -10253,32 +10193,34 @@
       <c r="A118" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B118" s="110" t="s">
+      <c r="B118" s="122" t="s">
         <v>617</v>
       </c>
-      <c r="C118" s="111" t="s">
+      <c r="C118" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D118" s="87" t="s">
+      <c r="D118" s="111" t="s">
         <v>506</v>
       </c>
-      <c r="E118" s="8" t="s">
+      <c r="E118" s="113" t="s">
         <v>102</v>
       </c>
-      <c r="F118" s="16"/>
-      <c r="G118" s="8" t="s">
+      <c r="F118" s="112"/>
+      <c r="G118" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H118" s="8" t="s">
+      <c r="H118" s="113" t="s">
         <v>161</v>
       </c>
-      <c r="I118" s="8" t="s">
+      <c r="I118" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="J118" s="16" t="s">
+      <c r="J118" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K118" s="16"/>
+      <c r="K118" s="112" t="s">
+        <v>633</v>
+      </c>
       <c r="L118" s="16" t="s">
         <v>13</v>
       </c>
@@ -10287,32 +10229,34 @@
       <c r="A119" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B119" s="110" t="s">
+      <c r="B119" s="122" t="s">
         <v>617</v>
       </c>
-      <c r="C119" s="111" t="s">
+      <c r="C119" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D119" s="87" t="s">
+      <c r="D119" s="111" t="s">
         <v>506</v>
       </c>
-      <c r="E119" s="16" t="s">
+      <c r="E119" s="112" t="s">
         <v>186</v>
       </c>
-      <c r="F119" s="16"/>
-      <c r="G119" s="8" t="s">
+      <c r="F119" s="112"/>
+      <c r="G119" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H119" s="8" t="s">
+      <c r="H119" s="113" t="s">
         <v>169</v>
       </c>
-      <c r="I119" s="8" t="s">
+      <c r="I119" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="J119" s="16" t="s">
+      <c r="J119" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K119" s="16"/>
+      <c r="K119" s="112" t="s">
+        <v>633</v>
+      </c>
       <c r="L119" s="16" t="s">
         <v>13</v>
       </c>
@@ -10321,32 +10265,34 @@
       <c r="A120" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B120" s="110" t="s">
+      <c r="B120" s="122" t="s">
         <v>617</v>
       </c>
-      <c r="C120" s="111" t="s">
+      <c r="C120" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D120" s="87" t="s">
+      <c r="D120" s="111" t="s">
         <v>506</v>
       </c>
-      <c r="E120" s="16" t="s">
+      <c r="E120" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="F120" s="16"/>
-      <c r="G120" s="8" t="s">
+      <c r="F120" s="112"/>
+      <c r="G120" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H120" s="16" t="s">
+      <c r="H120" s="112" t="s">
         <v>188</v>
       </c>
-      <c r="I120" s="16" t="s">
+      <c r="I120" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="J120" s="16" t="s">
+      <c r="J120" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K120" s="16"/>
+      <c r="K120" s="112" t="s">
+        <v>633</v>
+      </c>
       <c r="L120" s="16" t="s">
         <v>13</v>
       </c>
@@ -10355,32 +10301,34 @@
       <c r="A121" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B121" s="110" t="s">
+      <c r="B121" s="122" t="s">
         <v>617</v>
       </c>
-      <c r="C121" s="111" t="s">
+      <c r="C121" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D121" s="87" t="s">
+      <c r="D121" s="111" t="s">
         <v>506</v>
       </c>
-      <c r="E121" s="16" t="s">
+      <c r="E121" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="F121" s="16"/>
-      <c r="G121" s="8" t="s">
+      <c r="F121" s="112"/>
+      <c r="G121" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H121" s="8" t="s">
+      <c r="H121" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="I121" s="8" t="s">
+      <c r="I121" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="J121" s="16" t="s">
+      <c r="J121" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K121" s="16"/>
+      <c r="K121" s="112" t="s">
+        <v>633</v>
+      </c>
       <c r="L121" s="16" t="s">
         <v>52</v>
       </c>
@@ -10389,32 +10337,34 @@
       <c r="A122" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B122" s="110" t="s">
+      <c r="B122" s="122" t="s">
         <v>617</v>
       </c>
-      <c r="C122" s="111" t="s">
+      <c r="C122" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D122" s="87" t="s">
+      <c r="D122" s="111" t="s">
         <v>506</v>
       </c>
-      <c r="E122" s="16" t="s">
+      <c r="E122" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="F122" s="16"/>
-      <c r="G122" s="8" t="s">
+      <c r="F122" s="112"/>
+      <c r="G122" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H122" s="8" t="s">
+      <c r="H122" s="113" t="s">
         <v>191</v>
       </c>
-      <c r="I122" s="16" t="s">
+      <c r="I122" s="112" t="s">
         <v>124</v>
       </c>
-      <c r="J122" s="16" t="s">
+      <c r="J122" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="K122" s="16"/>
+      <c r="K122" s="112" t="s">
+        <v>633</v>
+      </c>
       <c r="L122" s="16" t="s">
         <v>125</v>
       </c>
@@ -10423,30 +10373,32 @@
       <c r="A123" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B123" s="110"/>
-      <c r="C123" s="111" t="s">
+      <c r="B123" s="122"/>
+      <c r="C123" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D123" s="87" t="s">
+      <c r="D123" s="111" t="s">
         <v>507</v>
       </c>
-      <c r="E123" s="16" t="s">
+      <c r="E123" s="112" t="s">
         <v>193</v>
       </c>
-      <c r="F123" s="16"/>
-      <c r="G123" s="16" t="s">
+      <c r="F123" s="112"/>
+      <c r="G123" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="H123" s="16" t="s">
+      <c r="H123" s="112" t="s">
         <v>482</v>
       </c>
-      <c r="I123" s="16" t="s">
+      <c r="I123" s="112" t="s">
         <v>481</v>
       </c>
-      <c r="J123" s="16" t="s">
+      <c r="J123" s="112" t="s">
         <v>194</v>
       </c>
-      <c r="K123" s="16"/>
+      <c r="K123" s="112" t="s">
+        <v>621</v>
+      </c>
       <c r="L123" s="16" t="s">
         <v>13</v>
       </c>
@@ -10455,30 +10407,32 @@
       <c r="A124" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B124" s="110"/>
-      <c r="C124" s="111" t="s">
+      <c r="B124" s="122"/>
+      <c r="C124" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D124" s="87" t="s">
+      <c r="D124" s="111" t="s">
         <v>507</v>
       </c>
-      <c r="E124" s="16" t="s">
+      <c r="E124" s="112" t="s">
         <v>195</v>
       </c>
-      <c r="F124" s="16"/>
-      <c r="G124" s="16" t="s">
+      <c r="F124" s="112"/>
+      <c r="G124" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="16" t="s">
+      <c r="H124" s="112" t="s">
         <v>482</v>
       </c>
-      <c r="I124" s="16" t="s">
+      <c r="I124" s="112" t="s">
         <v>481</v>
       </c>
-      <c r="J124" s="16" t="s">
+      <c r="J124" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="K124" s="16"/>
+      <c r="K124" s="112" t="s">
+        <v>621</v>
+      </c>
       <c r="L124" s="16" t="s">
         <v>13</v>
       </c>
@@ -10487,30 +10441,32 @@
       <c r="A125" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B125" s="110"/>
-      <c r="C125" s="111" t="s">
+      <c r="B125" s="122"/>
+      <c r="C125" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D125" s="87" t="s">
+      <c r="D125" s="111" t="s">
         <v>507</v>
       </c>
-      <c r="E125" s="16" t="s">
+      <c r="E125" s="112" t="s">
         <v>196</v>
       </c>
-      <c r="F125" s="16"/>
-      <c r="G125" s="16" t="s">
+      <c r="F125" s="112"/>
+      <c r="G125" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="H125" s="16" t="s">
+      <c r="H125" s="112" t="s">
         <v>482</v>
       </c>
-      <c r="I125" s="16" t="s">
+      <c r="I125" s="112" t="s">
         <v>481</v>
       </c>
-      <c r="J125" s="16" t="s">
+      <c r="J125" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="K125" s="15"/>
+      <c r="K125" s="112" t="s">
+        <v>621</v>
+      </c>
       <c r="L125" s="16" t="s">
         <v>13</v>
       </c>
@@ -10519,32 +10475,34 @@
       <c r="A126" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B126" s="110"/>
-      <c r="C126" s="111" t="s">
+      <c r="B126" s="122"/>
+      <c r="C126" s="122" t="s">
         <v>492</v>
       </c>
-      <c r="D126" s="87" t="s">
+      <c r="D126" s="111" t="s">
         <v>507</v>
       </c>
-      <c r="E126" s="16" t="s">
+      <c r="E126" s="112" t="s">
         <v>197</v>
       </c>
-      <c r="F126" s="16" t="s">
+      <c r="F126" s="112" t="s">
         <v>198</v>
       </c>
-      <c r="G126" s="16" t="s">
+      <c r="G126" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="H126" s="16" t="s">
+      <c r="H126" s="112" t="s">
         <v>482</v>
       </c>
-      <c r="I126" s="16" t="s">
+      <c r="I126" s="112" t="s">
         <v>481</v>
       </c>
-      <c r="J126" s="16" t="s">
+      <c r="J126" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="K126" s="16"/>
+      <c r="K126" s="112" t="s">
+        <v>622</v>
+      </c>
       <c r="L126" s="16" t="s">
         <v>21</v>
       </c>
@@ -10553,31 +10511,33 @@
       <c r="A127" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B127" s="110"/>
-      <c r="C127" s="111" t="s">
+      <c r="B127" s="62"/>
+      <c r="C127" s="62" t="s">
         <v>492</v>
       </c>
-      <c r="D127" s="87" t="s">
+      <c r="D127" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="E127" s="16" t="s">
+      <c r="E127" s="61" t="s">
         <v>483</v>
       </c>
-      <c r="F127" s="16"/>
-      <c r="G127" s="16" t="s">
+      <c r="F127" s="61"/>
+      <c r="G127" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="H127" s="16" t="s">
+      <c r="H127" s="61" t="s">
         <v>482</v>
       </c>
-      <c r="I127" s="16" t="s">
+      <c r="I127" s="61" t="s">
         <v>481</v>
       </c>
-      <c r="J127" s="16" t="s">
+      <c r="J127" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="K127" s="16"/>
-      <c r="L127" s="16" t="s">
+      <c r="K127" s="112" t="s">
+        <v>621</v>
+      </c>
+      <c r="L127" s="61" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10585,30 +10545,32 @@
       <c r="A128" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B128" s="110"/>
-      <c r="C128" s="111" t="s">
+      <c r="B128" s="62"/>
+      <c r="C128" s="62" t="s">
         <v>492</v>
       </c>
-      <c r="D128" s="87" t="s">
+      <c r="D128" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="E128" s="16" t="s">
+      <c r="E128" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="F128" s="16"/>
-      <c r="G128" s="16" t="s">
+      <c r="F128" s="61"/>
+      <c r="G128" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="H128" s="16" t="s">
+      <c r="H128" s="61" t="s">
         <v>482</v>
       </c>
-      <c r="I128" s="16" t="s">
+      <c r="I128" s="61" t="s">
         <v>481</v>
       </c>
-      <c r="J128" s="16" t="s">
+      <c r="J128" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="K128" s="16"/>
+      <c r="K128" s="112" t="s">
+        <v>623</v>
+      </c>
       <c r="L128" s="16" t="s">
         <v>13</v>
       </c>
@@ -10617,30 +10579,32 @@
       <c r="A129" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B129" s="110"/>
-      <c r="C129" s="111" t="s">
+      <c r="B129" s="62"/>
+      <c r="C129" s="62" t="s">
         <v>492</v>
       </c>
-      <c r="D129" s="87" t="s">
+      <c r="D129" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="E129" s="16" t="s">
+      <c r="E129" s="61" t="s">
         <v>201</v>
       </c>
-      <c r="F129" s="16"/>
-      <c r="G129" s="16" t="s">
+      <c r="F129" s="61"/>
+      <c r="G129" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="H129" s="16" t="s">
+      <c r="H129" s="61" t="s">
         <v>482</v>
       </c>
-      <c r="I129" s="16" t="s">
+      <c r="I129" s="61" t="s">
         <v>481</v>
       </c>
-      <c r="J129" s="16" t="s">
+      <c r="J129" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="K129" s="16"/>
+      <c r="K129" s="112" t="s">
+        <v>624</v>
+      </c>
       <c r="L129" s="16" t="s">
         <v>13</v>
       </c>
@@ -10649,16 +10613,16 @@
       <c r="A130" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B130" s="69" t="s">
+      <c r="B130" s="61" t="s">
         <v>202</v>
       </c>
-      <c r="C130" s="111" t="s">
+      <c r="C130" s="62" t="s">
         <v>492</v>
       </c>
-      <c r="D130" s="87" t="s">
+      <c r="D130" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="E130" s="16" t="s">
+      <c r="E130" s="61" t="s">
         <v>203</v>
       </c>
       <c r="F130" s="61" t="s">
@@ -10671,48 +10635,52 @@
       <c r="I130" s="61" t="s">
         <v>481</v>
       </c>
-      <c r="J130" s="16" t="s">
+      <c r="J130" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="K130" s="16"/>
-      <c r="L130" s="16"/>
+      <c r="K130" s="61" t="s">
+        <v>625</v>
+      </c>
+      <c r="L130" s="61"/>
     </row>
     <row r="131" spans="1:12" ht="56">
       <c r="A131" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B131" s="75" t="s">
+      <c r="B131" s="120" t="s">
         <v>207</v>
       </c>
-      <c r="C131" s="111" t="s">
+      <c r="C131" s="62" t="s">
         <v>492</v>
       </c>
-      <c r="D131" s="87" t="s">
+      <c r="D131" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="E131" s="77" t="s">
+      <c r="E131" s="123" t="s">
         <v>208</v>
       </c>
-      <c r="F131" s="16"/>
-      <c r="G131" s="16"/>
-      <c r="H131" s="16"/>
-      <c r="I131" s="16"/>
-      <c r="J131" s="16"/>
-      <c r="K131" s="16"/>
+      <c r="F131" s="61"/>
+      <c r="G131" s="61"/>
+      <c r="H131" s="61"/>
+      <c r="I131" s="61"/>
+      <c r="J131" s="61"/>
+      <c r="K131" s="61" t="s">
+        <v>626</v>
+      </c>
       <c r="L131" s="16"/>
     </row>
     <row r="132" spans="1:12" ht="28">
       <c r="A132" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B132" s="112"/>
-      <c r="C132" s="91" t="s">
+      <c r="B132" s="129"/>
+      <c r="C132" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D132" s="91" t="s">
+      <c r="D132" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E132" s="106" t="s">
+      <c r="E132" s="104" t="s">
         <v>516</v>
       </c>
       <c r="F132" s="16" t="s">
@@ -10730,27 +10698,29 @@
       <c r="J132" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K132" s="16"/>
+      <c r="K132" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L132" s="16"/>
     </row>
     <row r="133" spans="1:12" ht="37.5">
       <c r="A133" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B133" s="112"/>
-      <c r="C133" s="91" t="s">
+      <c r="B133" s="129"/>
+      <c r="C133" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D133" s="91" t="s">
+      <c r="D133" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E133" s="113" t="s">
+      <c r="E133" s="106" t="s">
         <v>519</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="G133" s="88" t="s">
+      <c r="G133" s="86" t="s">
         <v>47</v>
       </c>
       <c r="H133" s="2" t="s">
@@ -10762,28 +10732,30 @@
       <c r="J133" s="61" t="s">
         <v>530</v>
       </c>
-      <c r="K133" s="16"/>
+      <c r="K133" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L133" s="16"/>
     </row>
     <row r="134" spans="1:12" ht="28">
       <c r="A134" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B134" s="112"/>
-      <c r="C134" s="91" t="s">
+      <c r="B134" s="129"/>
+      <c r="C134" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D134" s="91" t="s">
+      <c r="D134" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E134" s="106" t="s">
+      <c r="E134" s="104" t="s">
         <v>523</v>
       </c>
       <c r="F134" s="16"/>
       <c r="G134" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="H134" s="94" t="s">
+      <c r="H134" s="92" t="s">
         <v>529</v>
       </c>
       <c r="I134" s="16" t="s">
@@ -10792,24 +10764,26 @@
       <c r="J134" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K134" s="16"/>
+      <c r="K134" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L134" s="16"/>
     </row>
     <row r="135" spans="1:12" ht="28">
       <c r="A135" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B135" s="112"/>
-      <c r="C135" s="91" t="s">
+      <c r="B135" s="129"/>
+      <c r="C135" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D135" s="91" t="s">
+      <c r="D135" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E135" s="113" t="s">
+      <c r="E135" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="F135" s="88"/>
+      <c r="F135" s="86"/>
       <c r="G135" s="16" t="s">
         <v>47</v>
       </c>
@@ -10822,28 +10796,30 @@
       <c r="J135" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K135" s="16"/>
+      <c r="K135" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L135" s="16"/>
     </row>
     <row r="136" spans="1:12" ht="28">
       <c r="A136" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B136" s="112"/>
-      <c r="C136" s="91" t="s">
+      <c r="B136" s="129"/>
+      <c r="C136" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D136" s="91" t="s">
+      <c r="D136" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E136" s="106" t="s">
+      <c r="E136" s="104" t="s">
         <v>151</v>
       </c>
       <c r="F136" s="16"/>
-      <c r="G136" s="90" t="s">
+      <c r="G136" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="H136" s="89" t="s">
+      <c r="H136" s="87" t="s">
         <v>26</v>
       </c>
       <c r="I136" s="16" t="s">
@@ -10852,21 +10828,23 @@
       <c r="J136" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K136" s="16"/>
+      <c r="K136" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L136" s="16"/>
     </row>
     <row r="137" spans="1:12" ht="28">
       <c r="A137" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B137" s="112"/>
-      <c r="C137" s="91" t="s">
+      <c r="B137" s="129"/>
+      <c r="C137" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D137" s="91" t="s">
+      <c r="D137" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E137" s="106" t="s">
+      <c r="E137" s="104" t="s">
         <v>524</v>
       </c>
       <c r="F137" s="16"/>
@@ -10882,21 +10860,23 @@
       <c r="J137" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K137" s="16"/>
+      <c r="K137" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L137" s="16"/>
     </row>
     <row r="138" spans="1:12" ht="28">
       <c r="A138" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B138" s="112"/>
-      <c r="C138" s="91" t="s">
+      <c r="B138" s="129"/>
+      <c r="C138" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D138" s="91" t="s">
+      <c r="D138" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E138" s="106" t="s">
+      <c r="E138" s="104" t="s">
         <v>368</v>
       </c>
       <c r="F138" s="16"/>
@@ -10912,21 +10892,23 @@
       <c r="J138" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K138" s="16"/>
+      <c r="K138" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L138" s="16"/>
     </row>
     <row r="139" spans="1:12" ht="28">
       <c r="A139" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B139" s="112"/>
-      <c r="C139" s="91" t="s">
+      <c r="B139" s="129"/>
+      <c r="C139" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D139" s="91" t="s">
+      <c r="D139" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E139" s="106" t="s">
+      <c r="E139" s="104" t="s">
         <v>525</v>
       </c>
       <c r="F139" s="16"/>
@@ -10942,21 +10924,23 @@
       <c r="J139" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K139" s="16"/>
+      <c r="K139" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L139" s="16"/>
     </row>
     <row r="140" spans="1:12" ht="28">
       <c r="A140" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B140" s="112"/>
-      <c r="C140" s="91" t="s">
+      <c r="B140" s="129"/>
+      <c r="C140" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D140" s="91" t="s">
+      <c r="D140" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E140" s="106" t="s">
+      <c r="E140" s="104" t="s">
         <v>526</v>
       </c>
       <c r="F140" s="16"/>
@@ -10972,21 +10956,23 @@
       <c r="J140" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K140" s="16"/>
+      <c r="K140" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L140" s="16"/>
     </row>
     <row r="141" spans="1:12" ht="28">
       <c r="A141" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B141" s="112"/>
-      <c r="C141" s="91" t="s">
+      <c r="B141" s="129"/>
+      <c r="C141" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D141" s="91" t="s">
+      <c r="D141" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E141" s="106" t="s">
+      <c r="E141" s="104" t="s">
         <v>527</v>
       </c>
       <c r="F141" s="16"/>
@@ -11002,21 +10988,23 @@
       <c r="J141" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K141" s="16"/>
+      <c r="K141" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L141" s="16"/>
     </row>
     <row r="142" spans="1:12" ht="28">
       <c r="A142" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B142" s="112"/>
-      <c r="C142" s="91" t="s">
+      <c r="B142" s="129"/>
+      <c r="C142" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D142" s="91" t="s">
+      <c r="D142" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E142" s="106" t="s">
+      <c r="E142" s="104" t="s">
         <v>528</v>
       </c>
       <c r="F142" s="16"/>
@@ -11032,21 +11020,23 @@
       <c r="J142" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K142" s="16"/>
+      <c r="K142" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L142" s="16"/>
     </row>
     <row r="143" spans="1:12" ht="28">
       <c r="A143" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B143" s="112"/>
-      <c r="C143" s="91" t="s">
+      <c r="B143" s="129"/>
+      <c r="C143" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D143" s="91" t="s">
+      <c r="D143" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E143" s="106" t="s">
+      <c r="E143" s="104" t="s">
         <v>520</v>
       </c>
       <c r="F143" s="16"/>
@@ -11062,21 +11052,23 @@
       <c r="J143" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K143" s="16"/>
+      <c r="K143" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L143" s="16"/>
     </row>
     <row r="144" spans="1:12" ht="28">
       <c r="A144" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B144" s="112"/>
-      <c r="C144" s="91" t="s">
+      <c r="B144" s="129"/>
+      <c r="C144" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D144" s="91" t="s">
+      <c r="D144" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E144" s="106" t="s">
+      <c r="E144" s="104" t="s">
         <v>521</v>
       </c>
       <c r="F144" s="16"/>
@@ -11092,21 +11084,23 @@
       <c r="J144" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K144" s="16"/>
+      <c r="K144" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L144" s="16"/>
     </row>
     <row r="145" spans="1:12" ht="28">
       <c r="A145" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B145" s="112"/>
-      <c r="C145" s="91" t="s">
+      <c r="B145" s="129"/>
+      <c r="C145" s="89" t="s">
         <v>492</v>
       </c>
-      <c r="D145" s="91" t="s">
+      <c r="D145" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="E145" s="106" t="s">
+      <c r="E145" s="104" t="s">
         <v>18</v>
       </c>
       <c r="F145" s="16"/>
@@ -11122,25 +11116,27 @@
       <c r="J145" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K145" s="16"/>
+      <c r="K145" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="L145" s="16"/>
     </row>
     <row r="146" spans="1:12" ht="56">
       <c r="A146" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B146" s="73" t="s">
+      <c r="B146" s="110" t="s">
         <v>210</v>
       </c>
-      <c r="C146" s="87" t="s">
+      <c r="C146" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D146" s="87"/>
+      <c r="D146" s="85"/>
       <c r="E146" s="8" t="s">
         <v>211</v>
       </c>
       <c r="F146" s="43"/>
-      <c r="G146" s="79" t="s">
+      <c r="G146" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H146" s="43"/>
@@ -11155,13 +11151,13 @@
       <c r="A147" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B147" s="73" t="s">
+      <c r="B147" s="110" t="s">
         <v>210</v>
       </c>
-      <c r="C147" s="87" t="s">
+      <c r="C147" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D147" s="87" t="s">
+      <c r="D147" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E147" s="8" t="s">
@@ -11170,7 +11166,7 @@
       <c r="F147" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G147" s="79" t="s">
+      <c r="G147" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H147" s="8" t="s">
@@ -11193,13 +11189,13 @@
       <c r="A148" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B148" s="73" t="s">
+      <c r="B148" s="110" t="s">
         <v>210</v>
       </c>
-      <c r="C148" s="87" t="s">
+      <c r="C148" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D148" s="87" t="s">
+      <c r="D148" s="85" t="s">
         <v>508</v>
       </c>
       <c r="E148" s="8" t="s">
@@ -11208,7 +11204,7 @@
       <c r="F148" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="G148" s="79" t="s">
+      <c r="G148" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H148" s="8" t="s">
@@ -11229,22 +11225,22 @@
       <c r="A149" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B149" s="73" t="s">
+      <c r="B149" s="110" t="s">
         <v>210</v>
       </c>
-      <c r="C149" s="87" t="s">
+      <c r="C149" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D149" s="87" t="s">
+      <c r="D149" s="85" t="s">
         <v>508</v>
       </c>
-      <c r="E149" s="76" t="s">
+      <c r="E149" s="75" t="s">
         <v>38</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="G149" s="79" t="s">
+      <c r="G149" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H149" s="8" t="s">
@@ -11265,20 +11261,20 @@
       <c r="A150" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B150" s="73" t="s">
+      <c r="B150" s="110" t="s">
         <v>210</v>
       </c>
-      <c r="C150" s="87" t="s">
+      <c r="C150" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D150" s="114" t="s">
+      <c r="D150" s="107" t="s">
         <v>514</v>
       </c>
-      <c r="E150" s="106" t="s">
+      <c r="E150" s="104" t="s">
         <v>132</v>
       </c>
       <c r="F150" s="16"/>
-      <c r="G150" s="79" t="s">
+      <c r="G150" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H150" s="16" t="s">
@@ -11299,20 +11295,20 @@
       <c r="A151" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B151" s="73" t="s">
+      <c r="B151" s="110" t="s">
         <v>210</v>
       </c>
-      <c r="C151" s="87" t="s">
+      <c r="C151" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D151" s="114" t="s">
+      <c r="D151" s="107" t="s">
         <v>514</v>
       </c>
-      <c r="E151" s="106" t="s">
+      <c r="E151" s="104" t="s">
         <v>221</v>
       </c>
       <c r="F151" s="16"/>
-      <c r="G151" s="79" t="s">
+      <c r="G151" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H151" s="16" t="s">
@@ -11333,20 +11329,20 @@
       <c r="A152" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B152" s="73" t="s">
+      <c r="B152" s="110" t="s">
         <v>210</v>
       </c>
-      <c r="C152" s="87" t="s">
+      <c r="C152" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D152" s="114" t="s">
+      <c r="D152" s="107" t="s">
         <v>514</v>
       </c>
-      <c r="E152" s="106" t="s">
+      <c r="E152" s="104" t="s">
         <v>222</v>
       </c>
       <c r="F152" s="16"/>
-      <c r="G152" s="79" t="s">
+      <c r="G152" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H152" s="16" t="s">
@@ -11367,22 +11363,22 @@
       <c r="A153" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B153" s="73" t="s">
+      <c r="B153" s="111" t="s">
         <v>210</v>
       </c>
-      <c r="C153" s="87" t="s">
+      <c r="C153" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D153" s="114" t="s">
+      <c r="D153" s="107" t="s">
         <v>514</v>
       </c>
-      <c r="E153" s="81" t="s">
+      <c r="E153" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="F153" s="81" t="s">
+      <c r="F153" s="79" t="s">
         <v>225</v>
       </c>
-      <c r="G153" s="79" t="s">
+      <c r="G153" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H153" s="16" t="s">
@@ -11397,7 +11393,7 @@
       <c r="K153" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L153" s="80" t="s">
+      <c r="L153" s="78" t="s">
         <v>228</v>
       </c>
     </row>
@@ -11405,22 +11401,22 @@
       <c r="A154" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B154" s="73" t="s">
+      <c r="B154" s="111" t="s">
         <v>210</v>
       </c>
-      <c r="C154" s="87" t="s">
+      <c r="C154" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D154" s="114" t="s">
+      <c r="D154" s="107" t="s">
         <v>514</v>
       </c>
-      <c r="E154" s="81" t="s">
+      <c r="E154" s="79" t="s">
         <v>229</v>
       </c>
-      <c r="F154" s="81" t="s">
+      <c r="F154" s="79" t="s">
         <v>230</v>
       </c>
-      <c r="G154" s="79" t="s">
+      <c r="G154" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H154" s="16" t="s">
@@ -11435,7 +11431,7 @@
       <c r="K154" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L154" s="80" t="s">
+      <c r="L154" s="78" t="s">
         <v>231</v>
       </c>
     </row>
@@ -11443,22 +11439,22 @@
       <c r="A155" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B155" s="73" t="s">
+      <c r="B155" s="111" t="s">
         <v>210</v>
       </c>
-      <c r="C155" s="87" t="s">
+      <c r="C155" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D155" s="114" t="s">
+      <c r="D155" s="107" t="s">
         <v>514</v>
       </c>
-      <c r="E155" s="81" t="s">
+      <c r="E155" s="79" t="s">
         <v>232</v>
       </c>
-      <c r="F155" s="81" t="s">
+      <c r="F155" s="79" t="s">
         <v>233</v>
       </c>
-      <c r="G155" s="79" t="s">
+      <c r="G155" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H155" s="16" t="s">
@@ -11473,7 +11469,7 @@
       <c r="K155" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L155" s="80" t="s">
+      <c r="L155" s="78" t="s">
         <v>234</v>
       </c>
     </row>
@@ -11481,22 +11477,22 @@
       <c r="A156" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B156" s="73" t="s">
+      <c r="B156" s="111" t="s">
         <v>210</v>
       </c>
-      <c r="C156" s="87" t="s">
+      <c r="C156" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D156" s="114" t="s">
+      <c r="D156" s="107" t="s">
         <v>514</v>
       </c>
-      <c r="E156" s="81" t="s">
+      <c r="E156" s="79" t="s">
         <v>235</v>
       </c>
-      <c r="F156" s="81" t="s">
+      <c r="F156" s="79" t="s">
         <v>236</v>
       </c>
-      <c r="G156" s="79" t="s">
+      <c r="G156" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H156" s="16" t="s">
@@ -11511,7 +11507,7 @@
       <c r="K156" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L156" s="80" t="s">
+      <c r="L156" s="78" t="s">
         <v>237</v>
       </c>
     </row>
@@ -11519,22 +11515,22 @@
       <c r="A157" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B157" s="73" t="s">
+      <c r="B157" s="111" t="s">
         <v>210</v>
       </c>
-      <c r="C157" s="87" t="s">
+      <c r="C157" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D157" s="114" t="s">
+      <c r="D157" s="107" t="s">
         <v>514</v>
       </c>
-      <c r="E157" s="81" t="s">
+      <c r="E157" s="79" t="s">
         <v>238</v>
       </c>
-      <c r="F157" s="81" t="s">
+      <c r="F157" s="79" t="s">
         <v>239</v>
       </c>
-      <c r="G157" s="79" t="s">
+      <c r="G157" s="77" t="s">
         <v>212</v>
       </c>
       <c r="H157" s="16" t="s">
@@ -11549,643 +11545,643 @@
       <c r="K157" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L157" s="80" t="s">
+      <c r="L157" s="78" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="158" spans="1:12" ht="56">
-      <c r="A158" s="95" t="s">
+      <c r="A158" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B158" s="95" t="s">
+      <c r="B158" s="73" t="s">
         <v>466</v>
       </c>
-      <c r="C158" s="95" t="s">
+      <c r="C158" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D158" s="95"/>
-      <c r="E158" s="115" t="s">
+      <c r="D158" s="93"/>
+      <c r="E158" s="108" t="s">
         <v>467</v>
       </c>
-      <c r="F158" s="100"/>
-      <c r="G158" s="96" t="s">
+      <c r="F158" s="98"/>
+      <c r="G158" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H158" s="97"/>
-      <c r="I158" s="97"/>
-      <c r="J158" s="98"/>
-      <c r="K158" s="97"/>
-      <c r="L158" s="99"/>
+      <c r="H158" s="95"/>
+      <c r="I158" s="95"/>
+      <c r="J158" s="96"/>
+      <c r="K158" s="95"/>
+      <c r="L158" s="97"/>
     </row>
     <row r="159" spans="1:12" ht="56">
-      <c r="A159" s="95" t="s">
+      <c r="A159" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B159" s="95"/>
-      <c r="C159" s="95" t="s">
+      <c r="B159" s="73"/>
+      <c r="C159" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D159" s="116" t="s">
+      <c r="D159" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E159" s="100" t="s">
+      <c r="E159" s="98" t="s">
         <v>241</v>
       </c>
-      <c r="F159" s="100" t="s">
+      <c r="F159" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G159" s="96" t="s">
+      <c r="G159" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H159" s="97" t="s">
+      <c r="H159" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I159" s="97" t="s">
+      <c r="I159" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J159" s="98" t="s">
+      <c r="J159" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K159" s="97"/>
-      <c r="L159" s="99" t="s">
+      <c r="K159" s="95"/>
+      <c r="L159" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:12" ht="56">
-      <c r="A160" s="95" t="s">
+      <c r="A160" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B160" s="95"/>
-      <c r="C160" s="95" t="s">
+      <c r="B160" s="73"/>
+      <c r="C160" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D160" s="116" t="s">
+      <c r="D160" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E160" s="100" t="s">
+      <c r="E160" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="F160" s="100" t="s">
+      <c r="F160" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G160" s="96" t="s">
+      <c r="G160" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H160" s="97" t="s">
+      <c r="H160" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I160" s="97" t="s">
+      <c r="I160" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J160" s="98" t="s">
+      <c r="J160" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K160" s="97"/>
-      <c r="L160" s="99" t="s">
+      <c r="K160" s="95"/>
+      <c r="L160" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:12" ht="56">
-      <c r="A161" s="95" t="s">
+      <c r="A161" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B161" s="95"/>
-      <c r="C161" s="95" t="s">
+      <c r="B161" s="73"/>
+      <c r="C161" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D161" s="116" t="s">
+      <c r="D161" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E161" s="100" t="s">
+      <c r="E161" s="98" t="s">
         <v>244</v>
       </c>
-      <c r="F161" s="100" t="s">
+      <c r="F161" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G161" s="96" t="s">
+      <c r="G161" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H161" s="97" t="s">
+      <c r="H161" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I161" s="97" t="s">
+      <c r="I161" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J161" s="98" t="s">
+      <c r="J161" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K161" s="97"/>
-      <c r="L161" s="99" t="s">
+      <c r="K161" s="95"/>
+      <c r="L161" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="162" spans="1:12" ht="56">
-      <c r="A162" s="95" t="s">
+      <c r="A162" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B162" s="95"/>
-      <c r="C162" s="95" t="s">
+      <c r="B162" s="73"/>
+      <c r="C162" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D162" s="116" t="s">
+      <c r="D162" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E162" s="100" t="s">
+      <c r="E162" s="98" t="s">
         <v>245</v>
       </c>
-      <c r="F162" s="100" t="s">
+      <c r="F162" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G162" s="96" t="s">
+      <c r="G162" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H162" s="97" t="s">
+      <c r="H162" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I162" s="97" t="s">
+      <c r="I162" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J162" s="98" t="s">
+      <c r="J162" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K162" s="97"/>
-      <c r="L162" s="99" t="s">
+      <c r="K162" s="95"/>
+      <c r="L162" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:12" ht="56">
-      <c r="A163" s="95" t="s">
+      <c r="A163" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B163" s="95"/>
-      <c r="C163" s="95" t="s">
+      <c r="B163" s="73"/>
+      <c r="C163" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D163" s="116" t="s">
+      <c r="D163" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E163" s="100" t="s">
+      <c r="E163" s="98" t="s">
         <v>246</v>
       </c>
-      <c r="F163" s="100" t="s">
+      <c r="F163" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G163" s="96" t="s">
+      <c r="G163" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H163" s="97" t="s">
+      <c r="H163" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I163" s="97" t="s">
+      <c r="I163" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J163" s="98" t="s">
+      <c r="J163" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K163" s="97"/>
-      <c r="L163" s="99" t="s">
+      <c r="K163" s="95"/>
+      <c r="L163" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:12" ht="56">
-      <c r="A164" s="95" t="s">
+      <c r="A164" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B164" s="95"/>
-      <c r="C164" s="95" t="s">
+      <c r="B164" s="73"/>
+      <c r="C164" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D164" s="116" t="s">
+      <c r="D164" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E164" s="100" t="s">
+      <c r="E164" s="98" t="s">
         <v>247</v>
       </c>
-      <c r="F164" s="100" t="s">
+      <c r="F164" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G164" s="96" t="s">
+      <c r="G164" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H164" s="97" t="s">
+      <c r="H164" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I164" s="97" t="s">
+      <c r="I164" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J164" s="98" t="s">
+      <c r="J164" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K164" s="97"/>
-      <c r="L164" s="99" t="s">
+      <c r="K164" s="95"/>
+      <c r="L164" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="56">
-      <c r="A165" s="95" t="s">
+      <c r="A165" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B165" s="95"/>
-      <c r="C165" s="95" t="s">
+      <c r="B165" s="73"/>
+      <c r="C165" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D165" s="116" t="s">
+      <c r="D165" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E165" s="100" t="s">
+      <c r="E165" s="98" t="s">
         <v>248</v>
       </c>
-      <c r="F165" s="100" t="s">
+      <c r="F165" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G165" s="96" t="s">
+      <c r="G165" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H165" s="97" t="s">
+      <c r="H165" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I165" s="97" t="s">
+      <c r="I165" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J165" s="98" t="s">
+      <c r="J165" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K165" s="97"/>
-      <c r="L165" s="99" t="s">
+      <c r="K165" s="95"/>
+      <c r="L165" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="56">
-      <c r="A166" s="95" t="s">
+      <c r="A166" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B166" s="95"/>
-      <c r="C166" s="95" t="s">
+      <c r="B166" s="73"/>
+      <c r="C166" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D166" s="116" t="s">
+      <c r="D166" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E166" s="100" t="s">
+      <c r="E166" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="F166" s="100" t="s">
+      <c r="F166" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G166" s="96" t="s">
+      <c r="G166" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H166" s="97" t="s">
+      <c r="H166" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I166" s="97" t="s">
+      <c r="I166" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J166" s="98" t="s">
+      <c r="J166" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K166" s="97"/>
-      <c r="L166" s="99" t="s">
+      <c r="K166" s="95"/>
+      <c r="L166" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="167" spans="1:12" ht="56">
-      <c r="A167" s="95" t="s">
+      <c r="A167" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B167" s="95"/>
-      <c r="C167" s="95" t="s">
+      <c r="B167" s="73"/>
+      <c r="C167" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D167" s="116" t="s">
+      <c r="D167" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E167" s="100" t="s">
+      <c r="E167" s="98" t="s">
         <v>250</v>
       </c>
-      <c r="F167" s="100" t="s">
+      <c r="F167" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="G167" s="96" t="s">
+      <c r="G167" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H167" s="97" t="s">
+      <c r="H167" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I167" s="97" t="s">
+      <c r="I167" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J167" s="98" t="s">
+      <c r="J167" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K167" s="97"/>
-      <c r="L167" s="99" t="s">
+      <c r="K167" s="95"/>
+      <c r="L167" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:12" ht="56">
-      <c r="A168" s="95" t="s">
+      <c r="A168" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B168" s="95"/>
-      <c r="C168" s="95" t="s">
+      <c r="B168" s="73"/>
+      <c r="C168" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D168" s="116" t="s">
+      <c r="D168" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E168" s="101" t="s">
+      <c r="E168" s="99" t="s">
         <v>232</v>
       </c>
-      <c r="F168" s="102" t="s">
+      <c r="F168" s="100" t="s">
         <v>251</v>
       </c>
-      <c r="G168" s="96" t="s">
+      <c r="G168" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H168" s="97" t="s">
+      <c r="H168" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I168" s="97" t="s">
+      <c r="I168" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J168" s="98" t="s">
+      <c r="J168" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K168" s="97"/>
-      <c r="L168" s="99" t="s">
+      <c r="K168" s="95"/>
+      <c r="L168" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="169" spans="1:12" ht="56">
-      <c r="A169" s="95" t="s">
+      <c r="A169" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B169" s="95"/>
-      <c r="C169" s="95" t="s">
+      <c r="B169" s="73"/>
+      <c r="C169" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D169" s="116" t="s">
+      <c r="D169" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E169" s="101" t="s">
+      <c r="E169" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="F169" s="102" t="s">
+      <c r="F169" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="G169" s="96" t="s">
+      <c r="G169" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H169" s="97" t="s">
+      <c r="H169" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I169" s="97" t="s">
+      <c r="I169" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J169" s="98" t="s">
+      <c r="J169" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K169" s="97"/>
-      <c r="L169" s="99" t="s">
+      <c r="K169" s="95"/>
+      <c r="L169" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="56">
-      <c r="A170" s="95" t="s">
+      <c r="A170" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B170" s="95"/>
-      <c r="C170" s="95" t="s">
+      <c r="B170" s="73"/>
+      <c r="C170" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D170" s="116" t="s">
+      <c r="D170" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E170" s="101" t="s">
+      <c r="E170" s="99" t="s">
         <v>253</v>
       </c>
-      <c r="F170" s="102" t="s">
+      <c r="F170" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="G170" s="96" t="s">
+      <c r="G170" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H170" s="97" t="s">
+      <c r="H170" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I170" s="97" t="s">
+      <c r="I170" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J170" s="98" t="s">
+      <c r="J170" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K170" s="97"/>
-      <c r="L170" s="99" t="s">
+      <c r="K170" s="95"/>
+      <c r="L170" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="171" spans="1:12" ht="56">
-      <c r="A171" s="95" t="s">
+      <c r="A171" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B171" s="95"/>
-      <c r="C171" s="95" t="s">
+      <c r="B171" s="73"/>
+      <c r="C171" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D171" s="116" t="s">
+      <c r="D171" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E171" s="101" t="s">
+      <c r="E171" s="99" t="s">
         <v>254</v>
       </c>
-      <c r="F171" s="102" t="s">
+      <c r="F171" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="G171" s="96" t="s">
+      <c r="G171" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H171" s="97" t="s">
+      <c r="H171" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I171" s="97" t="s">
+      <c r="I171" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J171" s="98" t="s">
+      <c r="J171" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K171" s="97"/>
-      <c r="L171" s="99" t="s">
+      <c r="K171" s="95"/>
+      <c r="L171" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:12" ht="56">
-      <c r="A172" s="95" t="s">
+      <c r="A172" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B172" s="95"/>
-      <c r="C172" s="95" t="s">
+      <c r="B172" s="73"/>
+      <c r="C172" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D172" s="116" t="s">
+      <c r="D172" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E172" s="101" t="s">
+      <c r="E172" s="99" t="s">
         <v>255</v>
       </c>
-      <c r="F172" s="102" t="s">
+      <c r="F172" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="G172" s="96" t="s">
+      <c r="G172" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H172" s="97" t="s">
+      <c r="H172" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I172" s="97" t="s">
+      <c r="I172" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J172" s="98" t="s">
+      <c r="J172" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K172" s="97"/>
-      <c r="L172" s="99" t="s">
+      <c r="K172" s="95"/>
+      <c r="L172" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="173" spans="1:12" ht="56">
-      <c r="A173" s="95" t="s">
+      <c r="A173" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B173" s="95"/>
-      <c r="C173" s="95" t="s">
+      <c r="B173" s="73"/>
+      <c r="C173" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D173" s="116" t="s">
+      <c r="D173" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E173" s="101" t="s">
+      <c r="E173" s="99" t="s">
         <v>256</v>
       </c>
-      <c r="F173" s="102" t="s">
+      <c r="F173" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="G173" s="96" t="s">
+      <c r="G173" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H173" s="97" t="s">
+      <c r="H173" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I173" s="97" t="s">
+      <c r="I173" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J173" s="98" t="s">
+      <c r="J173" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K173" s="97"/>
-      <c r="L173" s="99" t="s">
+      <c r="K173" s="95"/>
+      <c r="L173" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:12" ht="56">
-      <c r="A174" s="95" t="s">
+      <c r="A174" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B174" s="95"/>
-      <c r="C174" s="95" t="s">
+      <c r="B174" s="73"/>
+      <c r="C174" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D174" s="116" t="s">
+      <c r="D174" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E174" s="101" t="s">
+      <c r="E174" s="99" t="s">
         <v>257</v>
       </c>
-      <c r="F174" s="102" t="s">
+      <c r="F174" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="G174" s="96" t="s">
+      <c r="G174" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H174" s="97" t="s">
+      <c r="H174" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I174" s="97" t="s">
+      <c r="I174" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J174" s="98" t="s">
+      <c r="J174" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K174" s="97"/>
-      <c r="L174" s="99" t="s">
+      <c r="K174" s="95"/>
+      <c r="L174" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:12" ht="56">
-      <c r="A175" s="95" t="s">
+      <c r="A175" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B175" s="95"/>
-      <c r="C175" s="95" t="s">
+      <c r="B175" s="73"/>
+      <c r="C175" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D175" s="116" t="s">
+      <c r="D175" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E175" s="101" t="s">
+      <c r="E175" s="99" t="s">
         <v>258</v>
       </c>
-      <c r="F175" s="102" t="s">
+      <c r="F175" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="G175" s="96" t="s">
+      <c r="G175" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H175" s="97" t="s">
+      <c r="H175" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I175" s="97" t="s">
+      <c r="I175" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J175" s="98" t="s">
+      <c r="J175" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K175" s="97"/>
-      <c r="L175" s="99" t="s">
+      <c r="K175" s="95"/>
+      <c r="L175" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:12" ht="56">
-      <c r="A176" s="95" t="s">
+      <c r="A176" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B176" s="95"/>
-      <c r="C176" s="95" t="s">
+      <c r="B176" s="73"/>
+      <c r="C176" s="93" t="s">
         <v>492</v>
       </c>
-      <c r="D176" s="116" t="s">
+      <c r="D176" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="E176" s="101" t="s">
+      <c r="E176" s="99" t="s">
         <v>238</v>
       </c>
-      <c r="F176" s="102" t="s">
+      <c r="F176" s="100" t="s">
         <v>259</v>
       </c>
-      <c r="G176" s="96" t="s">
+      <c r="G176" s="94" t="s">
         <v>212</v>
       </c>
-      <c r="H176" s="97" t="s">
+      <c r="H176" s="95" t="s">
         <v>468</v>
       </c>
-      <c r="I176" s="97" t="s">
+      <c r="I176" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J176" s="98" t="s">
+      <c r="J176" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="K176" s="97"/>
-      <c r="L176" s="99" t="s">
+      <c r="K176" s="95"/>
+      <c r="L176" s="97" t="s">
         <v>13</v>
       </c>
     </row>
@@ -12196,10 +12192,10 @@
       <c r="B177" s="73" t="s">
         <v>260</v>
       </c>
-      <c r="C177" s="87" t="s">
+      <c r="C177" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D177" s="87"/>
+      <c r="D177" s="85"/>
       <c r="E177" s="16"/>
       <c r="F177" s="16"/>
       <c r="G177" s="16"/>
@@ -12216,10 +12212,10 @@
       <c r="B178" s="73" t="s">
         <v>261</v>
       </c>
-      <c r="C178" s="87" t="s">
+      <c r="C178" s="85" t="s">
         <v>492</v>
       </c>
-      <c r="D178" s="87"/>
+      <c r="D178" s="85"/>
       <c r="E178" s="16"/>
       <c r="F178" s="16"/>
       <c r="G178" s="16"/>
@@ -12237,7 +12233,8 @@
     <hyperlink ref="F58" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -12251,10 +12248,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="101" t="s">
         <v>262</v>
       </c>
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="101" t="s">
         <v>491</v>
       </c>
     </row>
@@ -13590,22 +13587,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="90" t="s">
         <v>531</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="90" t="s">
         <v>532</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="90" t="s">
         <v>533</v>
       </c>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="90" t="s">
         <v>534</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="90" t="s">
         <v>535</v>
       </c>
-      <c r="F1" s="92" t="s">
+      <c r="F1" s="90" t="s">
         <v>536</v>
       </c>
     </row>
@@ -16986,11 +16983,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{3c9bec58-8084-492e-8360-0e1cfe36408c}" enabled="1" method="Standard" siteId="{f35a6974-607f-47d4-82d7-ff31d7dc53a5}" removed="0"/>
-  <clbl:label id="{6d787ab7-f295-424f-b8cc-e3116a0f8520}" enabled="0" method="" siteId="{6d787ab7-f295-424f-b8cc-e3116a0f8520}" removed="1"/>
-</clbl:labelList>
 </file>